--- a/public/plantilla-capacitaciones.xlsx
+++ b/public/plantilla-capacitaciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacitaciones" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,10 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-  </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +71,14 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
@@ -208,7 +213,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -275,8 +280,14 @@
         <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCCF6A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="25">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -535,6 +546,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -563,49 +598,58 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
@@ -620,13 +664,13 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,10 +678,10 @@
     <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -646,20 +690,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -671,31 +715,26 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -704,19 +743,19 @@
     <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -725,7 +764,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -740,96 +779,117 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -840,74 +900,6 @@
     <cellStyle name="Normal 6 2" xfId="5"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -1271,88 +1263,88 @@
   </cols>
   <sheetData>
     <row r="1" ht="40.05" customHeight="1" s="70">
-      <c r="D1" s="32" t="inlineStr">
+      <c r="D1" s="35" t="inlineStr">
         <is>
           <t>MATRIZ DE CAPACITACIÓN SG-SST</t>
         </is>
       </c>
     </row>
     <row r="2" ht="14.4" customHeight="1" s="70">
-      <c r="D2" s="34" t="n"/>
-      <c r="E2" s="35" t="n"/>
-      <c r="F2" s="35" t="n"/>
-      <c r="G2" s="35" t="n"/>
-      <c r="H2" s="35" t="n"/>
-      <c r="I2" s="35" t="n"/>
-      <c r="J2" s="35" t="n"/>
-      <c r="K2" s="35" t="n"/>
-      <c r="L2" s="35" t="n"/>
-      <c r="M2" s="35" t="n"/>
-      <c r="N2" s="35" t="n"/>
-      <c r="O2" s="35" t="n"/>
-      <c r="P2" s="35" t="n"/>
-      <c r="Q2" s="35" t="n"/>
+      <c r="D2" s="37" t="n"/>
+      <c r="E2" s="38" t="n"/>
+      <c r="F2" s="38" t="n"/>
+      <c r="G2" s="38" t="n"/>
+      <c r="H2" s="38" t="n"/>
+      <c r="I2" s="38" t="n"/>
+      <c r="J2" s="38" t="n"/>
+      <c r="K2" s="38" t="n"/>
+      <c r="L2" s="38" t="n"/>
+      <c r="M2" s="38" t="n"/>
+      <c r="N2" s="38" t="n"/>
+      <c r="O2" s="38" t="n"/>
+      <c r="P2" s="38" t="n"/>
+      <c r="Q2" s="38" t="n"/>
     </row>
     <row r="3" ht="4.95" customHeight="1" s="70">
       <c r="D3" s="67" t="n"/>
-      <c r="E3" s="27" t="n"/>
-      <c r="F3" s="27" t="n"/>
-      <c r="G3" s="27" t="n"/>
-      <c r="H3" s="27" t="n"/>
-      <c r="I3" s="27" t="n"/>
-      <c r="J3" s="27" t="n"/>
-      <c r="K3" s="27" t="n"/>
-      <c r="L3" s="27" t="n"/>
-      <c r="M3" s="27" t="n"/>
-      <c r="N3" s="27" t="n"/>
-      <c r="O3" s="27" t="n"/>
-      <c r="P3" s="27" t="n"/>
-      <c r="Q3" s="28" t="n"/>
+      <c r="E3" s="30" t="n"/>
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30" t="n"/>
+      <c r="H3" s="30" t="n"/>
+      <c r="I3" s="30" t="n"/>
+      <c r="J3" s="30" t="n"/>
+      <c r="K3" s="30" t="n"/>
+      <c r="L3" s="30" t="n"/>
+      <c r="M3" s="30" t="n"/>
+      <c r="N3" s="30" t="n"/>
+      <c r="O3" s="30" t="n"/>
+      <c r="P3" s="30" t="n"/>
+      <c r="Q3" s="31" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="70">
-      <c r="O4" s="50" t="inlineStr">
+      <c r="O4" s="53" t="inlineStr">
         <is>
           <t>CONTROL DOCUMENTAL</t>
         </is>
       </c>
-      <c r="P4" s="27" t="n"/>
-      <c r="Q4" s="28" t="n"/>
+      <c r="P4" s="30" t="n"/>
+      <c r="Q4" s="31" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="70">
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="40" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="N5" s="38" t="n"/>
+      <c r="N5" s="41" t="n"/>
       <c r="O5" s="5" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="P5" s="46" t="inlineStr">
+      <c r="P5" s="49" t="inlineStr">
         <is>
           <t>RYR-SS-005</t>
         </is>
       </c>
-      <c r="Q5" s="28" t="n"/>
+      <c r="Q5" s="31" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="70">
-      <c r="D6" s="41" t="inlineStr">
+      <c r="D6" s="44" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN.</t>
         </is>
       </c>
-      <c r="N6" s="38" t="n"/>
+      <c r="N6" s="41" t="n"/>
       <c r="O6" s="5" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="P6" s="46" t="n">
+      <c r="P6" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" s="28" t="n"/>
+      <c r="Q6" s="31" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="70">
       <c r="D7" s="79" t="n"/>
@@ -1371,12 +1363,12 @@
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="P7" s="46" t="inlineStr">
+      <c r="P7" s="49" t="inlineStr">
         <is>
           <t>04/10/2026</t>
         </is>
       </c>
-      <c r="Q7" s="28" t="n"/>
+      <c r="Q7" s="31" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="70">
       <c r="D8" s="71" t="n"/>
@@ -1395,223 +1387,223 @@
           <t>Página</t>
         </is>
       </c>
-      <c r="P8" s="46" t="inlineStr">
+      <c r="P8" s="49" t="inlineStr">
         <is>
           <t>1 de 1</t>
         </is>
       </c>
-      <c r="Q8" s="28" t="n"/>
+      <c r="Q8" s="31" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="70">
-      <c r="A9" s="54" t="inlineStr">
+      <c r="A9" s="103" t="inlineStr">
         <is>
           <t>Programa de capacitación del proyecto: programación, ejecución, cobertura y eficacia · Decreto 1072 de 2015 · Resolución 0312 de 2019</t>
         </is>
       </c>
-      <c r="B9" s="55" t="n"/>
-      <c r="C9" s="55" t="n"/>
-      <c r="D9" s="55" t="n"/>
-      <c r="E9" s="55" t="n"/>
-      <c r="F9" s="55" t="n"/>
-      <c r="G9" s="55" t="n"/>
-      <c r="H9" s="55" t="n"/>
-      <c r="I9" s="55" t="n"/>
-      <c r="J9" s="55" t="n"/>
-      <c r="K9" s="55" t="n"/>
-      <c r="L9" s="55" t="n"/>
-      <c r="M9" s="55" t="n"/>
-      <c r="N9" s="55" t="n"/>
-      <c r="O9" s="55" t="n"/>
-      <c r="P9" s="55" t="n"/>
-      <c r="Q9" s="56" t="n"/>
+      <c r="B9" s="115" t="n"/>
+      <c r="C9" s="115" t="n"/>
+      <c r="D9" s="115" t="n"/>
+      <c r="E9" s="115" t="n"/>
+      <c r="F9" s="115" t="n"/>
+      <c r="G9" s="115" t="n"/>
+      <c r="H9" s="115" t="n"/>
+      <c r="I9" s="115" t="n"/>
+      <c r="J9" s="115" t="n"/>
+      <c r="K9" s="115" t="n"/>
+      <c r="L9" s="115" t="n"/>
+      <c r="M9" s="115" t="n"/>
+      <c r="N9" s="115" t="n"/>
+      <c r="O9" s="115" t="n"/>
+      <c r="P9" s="115" t="n"/>
+      <c r="Q9" s="116" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1" s="70">
-      <c r="A10" s="51" t="inlineStr">
+      <c r="A10" s="54" t="inlineStr">
         <is>
           <t>1. DATOS DEL PROGRAMA</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="35" t="n"/>
-      <c r="H10" s="35" t="n"/>
-      <c r="I10" s="35" t="n"/>
-      <c r="J10" s="35" t="n"/>
-      <c r="K10" s="35" t="n"/>
-      <c r="L10" s="35" t="n"/>
-      <c r="M10" s="35" t="n"/>
-      <c r="N10" s="35" t="n"/>
-      <c r="O10" s="35" t="n"/>
-      <c r="P10" s="35" t="n"/>
-      <c r="Q10" s="44" t="n"/>
+      <c r="B10" s="38" t="n"/>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="38" t="n"/>
+      <c r="F10" s="38" t="n"/>
+      <c r="G10" s="38" t="n"/>
+      <c r="H10" s="38" t="n"/>
+      <c r="I10" s="38" t="n"/>
+      <c r="J10" s="38" t="n"/>
+      <c r="K10" s="38" t="n"/>
+      <c r="L10" s="38" t="n"/>
+      <c r="M10" s="38" t="n"/>
+      <c r="N10" s="38" t="n"/>
+      <c r="O10" s="38" t="n"/>
+      <c r="P10" s="38" t="n"/>
+      <c r="Q10" s="47" t="n"/>
     </row>
     <row r="11" ht="19.95" customHeight="1" s="70">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
       </c>
-      <c r="B11" s="28" t="n"/>
-      <c r="C11" s="47" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="28" t="n"/>
-      <c r="H11" s="30" t="inlineStr">
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="50" t="n"/>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="30" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="31" t="n"/>
+      <c r="H11" s="33" t="inlineStr">
         <is>
           <t>Contratista / Empresa</t>
         </is>
       </c>
-      <c r="I11" s="27" t="n"/>
-      <c r="J11" s="27" t="n"/>
-      <c r="K11" s="28" t="n"/>
-      <c r="L11" s="40" t="n"/>
-      <c r="M11" s="27" t="n"/>
-      <c r="N11" s="27" t="n"/>
-      <c r="O11" s="27" t="n"/>
-      <c r="P11" s="27" t="n"/>
-      <c r="Q11" s="28" t="n"/>
+      <c r="I11" s="30" t="n"/>
+      <c r="J11" s="30" t="n"/>
+      <c r="K11" s="31" t="n"/>
+      <c r="L11" s="43" t="n"/>
+      <c r="M11" s="30" t="n"/>
+      <c r="N11" s="30" t="n"/>
+      <c r="O11" s="30" t="n"/>
+      <c r="P11" s="30" t="n"/>
+      <c r="Q11" s="31" t="n"/>
     </row>
     <row r="12" ht="19.95" customHeight="1" s="70">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="40" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="28" t="n"/>
-      <c r="H12" s="30" t="inlineStr">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="43" t="n"/>
+      <c r="D12" s="30" t="n"/>
+      <c r="E12" s="30" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="33" t="inlineStr">
         <is>
           <t>Responsable del programa SST</t>
         </is>
       </c>
-      <c r="I12" s="27" t="n"/>
-      <c r="J12" s="27" t="n"/>
-      <c r="K12" s="28" t="n"/>
-      <c r="L12" s="40" t="n"/>
-      <c r="M12" s="27" t="n"/>
-      <c r="N12" s="28" t="n"/>
-      <c r="O12" s="30" t="inlineStr">
+      <c r="I12" s="30" t="n"/>
+      <c r="J12" s="30" t="n"/>
+      <c r="K12" s="31" t="n"/>
+      <c r="L12" s="43" t="n"/>
+      <c r="M12" s="30" t="n"/>
+      <c r="N12" s="31" t="n"/>
+      <c r="O12" s="33" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="P12" s="40" t="n"/>
-      <c r="Q12" s="28" t="n"/>
+      <c r="P12" s="43" t="n"/>
+      <c r="Q12" s="31" t="n"/>
     </row>
     <row r="13" ht="19.95" customHeight="1" s="70">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>Periodo evaluado — desde</t>
         </is>
       </c>
-      <c r="B13" s="28" t="n"/>
-      <c r="C13" s="45" t="n"/>
-      <c r="D13" s="30" t="inlineStr">
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="48" t="n"/>
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>hasta</t>
         </is>
       </c>
-      <c r="E13" s="45" t="n"/>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="28" t="n"/>
-      <c r="H13" s="30" t="inlineStr">
+      <c r="E13" s="48" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="31" t="n"/>
+      <c r="H13" s="33" t="inlineStr">
         <is>
           <t>Fecha de actualización</t>
         </is>
       </c>
-      <c r="I13" s="27" t="n"/>
-      <c r="J13" s="27" t="n"/>
-      <c r="K13" s="28" t="n"/>
-      <c r="L13" s="45" t="n"/>
-      <c r="M13" s="27" t="n"/>
-      <c r="N13" s="28" t="n"/>
-      <c r="Q13" s="42" t="n"/>
+      <c r="I13" s="30" t="n"/>
+      <c r="J13" s="30" t="n"/>
+      <c r="K13" s="31" t="n"/>
+      <c r="L13" s="48" t="n"/>
+      <c r="M13" s="30" t="n"/>
+      <c r="N13" s="31" t="n"/>
+      <c r="Q13" s="45" t="n"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="70">
-      <c r="A14" s="51" t="inlineStr">
+      <c r="A14" s="54" t="inlineStr">
         <is>
           <t>2. INDICADORES DEL PROGRAMA (se calculan solos con la matriz)</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
-      <c r="H14" s="35" t="n"/>
-      <c r="I14" s="35" t="n"/>
-      <c r="J14" s="35" t="n"/>
-      <c r="K14" s="35" t="n"/>
-      <c r="L14" s="35" t="n"/>
-      <c r="M14" s="35" t="n"/>
-      <c r="N14" s="35" t="n"/>
-      <c r="O14" s="35" t="n"/>
-      <c r="P14" s="35" t="n"/>
-      <c r="Q14" s="44" t="n"/>
+      <c r="B14" s="38" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="38" t="n"/>
+      <c r="F14" s="38" t="n"/>
+      <c r="G14" s="38" t="n"/>
+      <c r="H14" s="38" t="n"/>
+      <c r="I14" s="38" t="n"/>
+      <c r="J14" s="38" t="n"/>
+      <c r="K14" s="38" t="n"/>
+      <c r="L14" s="38" t="n"/>
+      <c r="M14" s="38" t="n"/>
+      <c r="N14" s="38" t="n"/>
+      <c r="O14" s="38" t="n"/>
+      <c r="P14" s="38" t="n"/>
+      <c r="Q14" s="47" t="n"/>
     </row>
     <row r="15" ht="27" customHeight="1" s="70">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Capacitaciones programadas</t>
         </is>
       </c>
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="B15" s="31" t="n"/>
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>Capacitaciones ejecutadas</t>
         </is>
       </c>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="31" t="inlineStr">
+      <c r="D15" s="31" t="n"/>
+      <c r="E15" s="34" t="inlineStr">
         <is>
           <t>% de cumplimiento</t>
         </is>
       </c>
-      <c r="F15" s="28" t="n"/>
-      <c r="G15" s="31" t="inlineStr">
+      <c r="F15" s="31" t="n"/>
+      <c r="G15" s="34" t="inlineStr">
         <is>
           <t>Meta de cumplimiento</t>
         </is>
       </c>
-      <c r="H15" s="31" t="inlineStr">
+      <c r="H15" s="34" t="inlineStr">
         <is>
           <t>Personas convocadas</t>
         </is>
       </c>
-      <c r="I15" s="28" t="n"/>
-      <c r="J15" s="31" t="inlineStr">
+      <c r="I15" s="31" t="n"/>
+      <c r="J15" s="34" t="inlineStr">
         <is>
           <t>Personas asistentes</t>
         </is>
       </c>
-      <c r="K15" s="28" t="n"/>
-      <c r="L15" s="31" t="inlineStr">
+      <c r="K15" s="31" t="n"/>
+      <c r="L15" s="34" t="inlineStr">
         <is>
           <t>Cobertura global</t>
         </is>
       </c>
-      <c r="M15" s="28" t="n"/>
-      <c r="N15" s="31" t="inlineStr">
+      <c r="M15" s="31" t="n"/>
+      <c r="N15" s="34" t="inlineStr">
         <is>
           <t>Meta de cobertura</t>
         </is>
       </c>
-      <c r="O15" s="28" t="n"/>
-      <c r="P15" s="31" t="inlineStr">
+      <c r="O15" s="31" t="n"/>
+      <c r="P15" s="34" t="inlineStr">
         <is>
           <t>Eficacia global</t>
         </is>
       </c>
-      <c r="Q15" s="31" t="inlineStr">
+      <c r="Q15" s="34" t="inlineStr">
         <is>
           <t>Meta de eficacia</t>
         </is>
@@ -1622,17 +1614,17 @@
         <f>COUNTA(B20:B34)</f>
         <v/>
       </c>
-      <c r="B16" s="28" t="n"/>
+      <c r="B16" s="31" t="n"/>
       <c r="C16" s="58">
         <f>COUNTIF(P20:P34,"Ejecutada")</f>
         <v/>
       </c>
-      <c r="D16" s="28" t="n"/>
-      <c r="E16" s="29">
+      <c r="D16" s="31" t="n"/>
+      <c r="E16" s="32">
         <f>IFERROR(C16/A16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="28" t="n"/>
+      <c r="F16" s="31" t="n"/>
       <c r="G16" s="59" t="n">
         <v>0.9</v>
       </c>
@@ -1640,22 +1632,22 @@
         <f>SUM(I20:I34)</f>
         <v/>
       </c>
-      <c r="I16" s="28" t="n"/>
+      <c r="I16" s="31" t="n"/>
       <c r="J16" s="58">
         <f>SUM(J20:J34)</f>
         <v/>
       </c>
-      <c r="K16" s="28" t="n"/>
-      <c r="L16" s="29">
+      <c r="K16" s="31" t="n"/>
+      <c r="L16" s="32">
         <f>IFERROR(J16/H16,"")</f>
         <v/>
       </c>
-      <c r="M16" s="28" t="n"/>
+      <c r="M16" s="31" t="n"/>
       <c r="N16" s="59" t="n">
         <v>0.8</v>
       </c>
-      <c r="O16" s="28" t="n"/>
-      <c r="P16" s="29">
+      <c r="O16" s="31" t="n"/>
+      <c r="P16" s="32">
         <f>IFERROR(SUM(M20:M34)/SUM(L20:L34),"")</f>
         <v/>
       </c>
@@ -1664,142 +1656,142 @@
       </c>
     </row>
     <row r="17" ht="19.95" customHeight="1" s="70">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>Estado del programa</t>
         </is>
       </c>
-      <c r="B17" s="28" t="n"/>
-      <c r="C17" s="45">
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="48">
         <f>IF(E16="","",IF(E16&gt;=G16,"✔ Cumple la meta de cumplimiento","✘ Por debajo de la meta de cumplimiento"))</f>
         <v/>
       </c>
-      <c r="D17" s="27" t="n"/>
-      <c r="E17" s="27" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="28" t="n"/>
-      <c r="H17" s="45">
+      <c r="D17" s="30" t="n"/>
+      <c r="E17" s="30" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="31" t="n"/>
+      <c r="H17" s="48">
         <f>IF(L16="","",IF(L16&gt;=N16,"✔ Cobertura en meta","✘ Cobertura por debajo de la meta"))</f>
         <v/>
       </c>
-      <c r="I17" s="27" t="n"/>
-      <c r="J17" s="27" t="n"/>
-      <c r="K17" s="28" t="n"/>
-      <c r="L17" s="45">
+      <c r="I17" s="30" t="n"/>
+      <c r="J17" s="30" t="n"/>
+      <c r="K17" s="31" t="n"/>
+      <c r="L17" s="48">
         <f>IF(P16="","",IF(P16&gt;=Q16,"✔ Eficacia en meta","✘ Eficacia por debajo de la meta"))</f>
         <v/>
       </c>
-      <c r="M17" s="27" t="n"/>
-      <c r="N17" s="27" t="n"/>
-      <c r="O17" s="27" t="n"/>
-      <c r="P17" s="27" t="n"/>
-      <c r="Q17" s="28" t="n"/>
+      <c r="M17" s="30" t="n"/>
+      <c r="N17" s="30" t="n"/>
+      <c r="O17" s="30" t="n"/>
+      <c r="P17" s="30" t="n"/>
+      <c r="Q17" s="31" t="n"/>
     </row>
     <row r="18" ht="16.5" customHeight="1" s="70">
-      <c r="A18" s="51" t="inlineStr">
+      <c r="A18" s="54" t="inlineStr">
         <is>
           <t>3. MATRIZ DE CAPACITACIÓN</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
-      <c r="G18" s="35" t="n"/>
-      <c r="H18" s="35" t="n"/>
-      <c r="I18" s="35" t="n"/>
-      <c r="J18" s="35" t="n"/>
-      <c r="K18" s="35" t="n"/>
-      <c r="L18" s="35" t="n"/>
-      <c r="M18" s="35" t="n"/>
-      <c r="N18" s="35" t="n"/>
-      <c r="O18" s="35" t="n"/>
-      <c r="P18" s="35" t="n"/>
-      <c r="Q18" s="44" t="n"/>
+      <c r="B18" s="38" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="38" t="n"/>
+      <c r="E18" s="38" t="n"/>
+      <c r="F18" s="38" t="n"/>
+      <c r="G18" s="38" t="n"/>
+      <c r="H18" s="38" t="n"/>
+      <c r="I18" s="38" t="n"/>
+      <c r="J18" s="38" t="n"/>
+      <c r="K18" s="38" t="n"/>
+      <c r="L18" s="38" t="n"/>
+      <c r="M18" s="38" t="n"/>
+      <c r="N18" s="38" t="n"/>
+      <c r="O18" s="38" t="n"/>
+      <c r="P18" s="38" t="n"/>
+      <c r="Q18" s="47" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1" s="70">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B19" s="31" t="inlineStr">
+      <c r="B19" s="34" t="inlineStr">
         <is>
           <t>Tema de la capacitación</t>
         </is>
       </c>
-      <c r="C19" s="31" t="inlineStr">
+      <c r="C19" s="34" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D19" s="31" t="inlineStr">
+      <c r="D19" s="34" t="inlineStr">
         <is>
           <t>Dirigida a</t>
         </is>
       </c>
-      <c r="E19" s="31" t="inlineStr">
+      <c r="E19" s="34" t="inlineStr">
         <is>
           <t>Fecha programada</t>
         </is>
       </c>
-      <c r="F19" s="31" t="inlineStr">
+      <c r="F19" s="34" t="inlineStr">
         <is>
           <t>Fecha ejecutada</t>
         </is>
       </c>
-      <c r="G19" s="31" t="inlineStr">
+      <c r="G19" s="34" t="inlineStr">
         <is>
           <t>Capacitador / entidad</t>
         </is>
       </c>
-      <c r="H19" s="31" t="inlineStr">
+      <c r="H19" s="34" t="inlineStr">
         <is>
           <t>Duración (h)</t>
         </is>
       </c>
-      <c r="I19" s="31" t="inlineStr">
+      <c r="I19" s="34" t="inlineStr">
         <is>
           <t>Personas convocadas</t>
         </is>
       </c>
-      <c r="J19" s="31" t="inlineStr">
+      <c r="J19" s="34" t="inlineStr">
         <is>
           <t>Personas asistentes</t>
         </is>
       </c>
-      <c r="K19" s="31" t="inlineStr">
+      <c r="K19" s="34" t="inlineStr">
         <is>
           <t>Cobertura %</t>
         </is>
       </c>
-      <c r="L19" s="31" t="inlineStr">
+      <c r="L19" s="34" t="inlineStr">
         <is>
           <t>Personas evaluadas</t>
         </is>
       </c>
-      <c r="M19" s="31" t="inlineStr">
+      <c r="M19" s="34" t="inlineStr">
         <is>
           <t>Personas aprobadas</t>
         </is>
       </c>
-      <c r="N19" s="31" t="inlineStr">
+      <c r="N19" s="34" t="inlineStr">
         <is>
           <t>Eficacia %</t>
         </is>
       </c>
-      <c r="O19" s="31" t="inlineStr">
+      <c r="O19" s="34" t="inlineStr">
         <is>
           <t>Lista de asistencia N°</t>
         </is>
       </c>
-      <c r="P19" s="31" t="inlineStr">
+      <c r="P19" s="34" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="Q19" s="31" t="inlineStr">
+      <c r="Q19" s="34" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -1809,406 +1801,406 @@
       <c r="A20" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="26" t="n"/>
-      <c r="C20" s="26" t="n"/>
-      <c r="D20" s="26" t="n"/>
-      <c r="E20" s="24" t="n"/>
-      <c r="F20" s="24" t="n"/>
-      <c r="G20" s="26" t="n"/>
+      <c r="B20" s="29" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="29" t="n"/>
       <c r="H20" s="57" t="n"/>
       <c r="I20" s="57" t="n"/>
       <c r="J20" s="57" t="n"/>
-      <c r="K20" s="25">
+      <c r="K20" s="28">
         <f>IFERROR(J20/I20,"")</f>
         <v/>
       </c>
       <c r="L20" s="57" t="n"/>
       <c r="M20" s="57" t="n"/>
-      <c r="N20" s="25">
+      <c r="N20" s="28">
         <f>IFERROR(M20/L20,"")</f>
         <v/>
       </c>
       <c r="O20" s="57" t="n"/>
       <c r="P20" s="57" t="n"/>
-      <c r="Q20" s="26" t="n"/>
+      <c r="Q20" s="29" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="70">
       <c r="A21" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="26" t="n"/>
-      <c r="C21" s="26" t="n"/>
-      <c r="D21" s="26" t="n"/>
-      <c r="E21" s="24" t="n"/>
-      <c r="F21" s="24" t="n"/>
-      <c r="G21" s="26" t="n"/>
+      <c r="B21" s="29" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="27" t="n"/>
+      <c r="G21" s="29" t="n"/>
       <c r="H21" s="57" t="n"/>
       <c r="I21" s="57" t="n"/>
       <c r="J21" s="57" t="n"/>
-      <c r="K21" s="25">
+      <c r="K21" s="28">
         <f>IFERROR(J21/I21,"")</f>
         <v/>
       </c>
       <c r="L21" s="57" t="n"/>
       <c r="M21" s="57" t="n"/>
-      <c r="N21" s="25">
+      <c r="N21" s="28">
         <f>IFERROR(M21/L21,"")</f>
         <v/>
       </c>
       <c r="O21" s="57" t="n"/>
       <c r="P21" s="57" t="n"/>
-      <c r="Q21" s="26" t="n"/>
+      <c r="Q21" s="29" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1" s="70">
       <c r="A22" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="26" t="n"/>
-      <c r="C22" s="26" t="n"/>
-      <c r="D22" s="26" t="n"/>
-      <c r="E22" s="24" t="n"/>
-      <c r="F22" s="24" t="n"/>
-      <c r="G22" s="26" t="n"/>
+      <c r="B22" s="29" t="n"/>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="27" t="n"/>
+      <c r="G22" s="29" t="n"/>
       <c r="H22" s="57" t="n"/>
       <c r="I22" s="57" t="n"/>
       <c r="J22" s="57" t="n"/>
-      <c r="K22" s="25">
+      <c r="K22" s="28">
         <f>IFERROR(J22/I22,"")</f>
         <v/>
       </c>
       <c r="L22" s="57" t="n"/>
       <c r="M22" s="57" t="n"/>
-      <c r="N22" s="25">
+      <c r="N22" s="28">
         <f>IFERROR(M22/L22,"")</f>
         <v/>
       </c>
       <c r="O22" s="57" t="n"/>
       <c r="P22" s="57" t="n"/>
-      <c r="Q22" s="26" t="n"/>
+      <c r="Q22" s="29" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="70">
       <c r="A23" s="57" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="26" t="n"/>
-      <c r="C23" s="26" t="n"/>
-      <c r="D23" s="26" t="n"/>
-      <c r="E23" s="24" t="n"/>
-      <c r="F23" s="24" t="n"/>
-      <c r="G23" s="26" t="n"/>
+      <c r="B23" s="29" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="27" t="n"/>
+      <c r="G23" s="29" t="n"/>
       <c r="H23" s="57" t="n"/>
       <c r="I23" s="57" t="n"/>
       <c r="J23" s="57" t="n"/>
-      <c r="K23" s="25">
+      <c r="K23" s="28">
         <f>IFERROR(J23/I23,"")</f>
         <v/>
       </c>
       <c r="L23" s="57" t="n"/>
       <c r="M23" s="57" t="n"/>
-      <c r="N23" s="25">
+      <c r="N23" s="28">
         <f>IFERROR(M23/L23,"")</f>
         <v/>
       </c>
       <c r="O23" s="57" t="n"/>
       <c r="P23" s="57" t="n"/>
-      <c r="Q23" s="26" t="n"/>
+      <c r="Q23" s="29" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="70">
       <c r="A24" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="26" t="n"/>
-      <c r="C24" s="26" t="n"/>
-      <c r="D24" s="26" t="n"/>
-      <c r="E24" s="24" t="n"/>
-      <c r="F24" s="24" t="n"/>
-      <c r="G24" s="26" t="n"/>
+      <c r="B24" s="29" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="27" t="n"/>
+      <c r="G24" s="29" t="n"/>
       <c r="H24" s="57" t="n"/>
       <c r="I24" s="57" t="n"/>
       <c r="J24" s="57" t="n"/>
-      <c r="K24" s="25">
+      <c r="K24" s="28">
         <f>IFERROR(J24/I24,"")</f>
         <v/>
       </c>
       <c r="L24" s="57" t="n"/>
       <c r="M24" s="57" t="n"/>
-      <c r="N24" s="25">
+      <c r="N24" s="28">
         <f>IFERROR(M24/L24,"")</f>
         <v/>
       </c>
       <c r="O24" s="57" t="n"/>
       <c r="P24" s="57" t="n"/>
-      <c r="Q24" s="26" t="n"/>
+      <c r="Q24" s="29" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="70">
       <c r="A25" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="26" t="n"/>
-      <c r="C25" s="26" t="n"/>
-      <c r="D25" s="26" t="n"/>
-      <c r="E25" s="24" t="n"/>
-      <c r="F25" s="24" t="n"/>
-      <c r="G25" s="26" t="n"/>
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="27" t="n"/>
+      <c r="G25" s="29" t="n"/>
       <c r="H25" s="57" t="n"/>
       <c r="I25" s="57" t="n"/>
       <c r="J25" s="57" t="n"/>
-      <c r="K25" s="25">
+      <c r="K25" s="28">
         <f>IFERROR(J25/I25,"")</f>
         <v/>
       </c>
       <c r="L25" s="57" t="n"/>
       <c r="M25" s="57" t="n"/>
-      <c r="N25" s="25">
+      <c r="N25" s="28">
         <f>IFERROR(M25/L25,"")</f>
         <v/>
       </c>
       <c r="O25" s="57" t="n"/>
       <c r="P25" s="57" t="n"/>
-      <c r="Q25" s="26" t="n"/>
+      <c r="Q25" s="29" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="70">
       <c r="A26" s="57" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="26" t="n"/>
-      <c r="C26" s="26" t="n"/>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="24" t="n"/>
-      <c r="F26" s="24" t="n"/>
-      <c r="G26" s="26" t="n"/>
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="29" t="n"/>
       <c r="H26" s="57" t="n"/>
       <c r="I26" s="57" t="n"/>
       <c r="J26" s="57" t="n"/>
-      <c r="K26" s="25">
+      <c r="K26" s="28">
         <f>IFERROR(J26/I26,"")</f>
         <v/>
       </c>
       <c r="L26" s="57" t="n"/>
       <c r="M26" s="57" t="n"/>
-      <c r="N26" s="25">
+      <c r="N26" s="28">
         <f>IFERROR(M26/L26,"")</f>
         <v/>
       </c>
       <c r="O26" s="57" t="n"/>
       <c r="P26" s="57" t="n"/>
-      <c r="Q26" s="26" t="n"/>
+      <c r="Q26" s="29" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="70">
       <c r="A27" s="57" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="26" t="n"/>
-      <c r="C27" s="26" t="n"/>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="24" t="n"/>
-      <c r="F27" s="24" t="n"/>
-      <c r="G27" s="26" t="n"/>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="27" t="n"/>
+      <c r="F27" s="27" t="n"/>
+      <c r="G27" s="29" t="n"/>
       <c r="H27" s="57" t="n"/>
       <c r="I27" s="57" t="n"/>
       <c r="J27" s="57" t="n"/>
-      <c r="K27" s="25">
+      <c r="K27" s="28">
         <f>IFERROR(J27/I27,"")</f>
         <v/>
       </c>
       <c r="L27" s="57" t="n"/>
       <c r="M27" s="57" t="n"/>
-      <c r="N27" s="25">
+      <c r="N27" s="28">
         <f>IFERROR(M27/L27,"")</f>
         <v/>
       </c>
       <c r="O27" s="57" t="n"/>
       <c r="P27" s="57" t="n"/>
-      <c r="Q27" s="26" t="n"/>
+      <c r="Q27" s="29" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="70">
       <c r="A28" s="57" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="26" t="n"/>
-      <c r="C28" s="26" t="n"/>
-      <c r="D28" s="26" t="n"/>
-      <c r="E28" s="24" t="n"/>
-      <c r="F28" s="24" t="n"/>
-      <c r="G28" s="26" t="n"/>
+      <c r="B28" s="29" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="27" t="n"/>
+      <c r="G28" s="29" t="n"/>
       <c r="H28" s="57" t="n"/>
       <c r="I28" s="57" t="n"/>
       <c r="J28" s="57" t="n"/>
-      <c r="K28" s="25">
+      <c r="K28" s="28">
         <f>IFERROR(J28/I28,"")</f>
         <v/>
       </c>
       <c r="L28" s="57" t="n"/>
       <c r="M28" s="57" t="n"/>
-      <c r="N28" s="25">
+      <c r="N28" s="28">
         <f>IFERROR(M28/L28,"")</f>
         <v/>
       </c>
       <c r="O28" s="57" t="n"/>
       <c r="P28" s="57" t="n"/>
-      <c r="Q28" s="26" t="n"/>
+      <c r="Q28" s="29" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="70">
       <c r="A29" s="57" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="26" t="n"/>
-      <c r="C29" s="26" t="n"/>
-      <c r="D29" s="26" t="n"/>
-      <c r="E29" s="24" t="n"/>
-      <c r="F29" s="24" t="n"/>
-      <c r="G29" s="26" t="n"/>
+      <c r="B29" s="29" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="27" t="n"/>
+      <c r="G29" s="29" t="n"/>
       <c r="H29" s="57" t="n"/>
       <c r="I29" s="57" t="n"/>
       <c r="J29" s="57" t="n"/>
-      <c r="K29" s="25">
+      <c r="K29" s="28">
         <f>IFERROR(J29/I29,"")</f>
         <v/>
       </c>
       <c r="L29" s="57" t="n"/>
       <c r="M29" s="57" t="n"/>
-      <c r="N29" s="25">
+      <c r="N29" s="28">
         <f>IFERROR(M29/L29,"")</f>
         <v/>
       </c>
       <c r="O29" s="57" t="n"/>
       <c r="P29" s="57" t="n"/>
-      <c r="Q29" s="26" t="n"/>
+      <c r="Q29" s="29" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="70">
       <c r="A30" s="57" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="26" t="n"/>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="26" t="n"/>
-      <c r="E30" s="24" t="n"/>
-      <c r="F30" s="24" t="n"/>
-      <c r="G30" s="26" t="n"/>
+      <c r="B30" s="29" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="27" t="n"/>
+      <c r="F30" s="27" t="n"/>
+      <c r="G30" s="29" t="n"/>
       <c r="H30" s="57" t="n"/>
       <c r="I30" s="57" t="n"/>
       <c r="J30" s="57" t="n"/>
-      <c r="K30" s="25">
+      <c r="K30" s="28">
         <f>IFERROR(J30/I30,"")</f>
         <v/>
       </c>
       <c r="L30" s="57" t="n"/>
       <c r="M30" s="57" t="n"/>
-      <c r="N30" s="25">
+      <c r="N30" s="28">
         <f>IFERROR(M30/L30,"")</f>
         <v/>
       </c>
       <c r="O30" s="57" t="n"/>
       <c r="P30" s="57" t="n"/>
-      <c r="Q30" s="26" t="n"/>
+      <c r="Q30" s="29" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="70">
       <c r="A31" s="57" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="26" t="n"/>
-      <c r="C31" s="26" t="n"/>
-      <c r="D31" s="26" t="n"/>
-      <c r="E31" s="24" t="n"/>
-      <c r="F31" s="24" t="n"/>
-      <c r="G31" s="26" t="n"/>
+      <c r="B31" s="29" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="27" t="n"/>
+      <c r="F31" s="27" t="n"/>
+      <c r="G31" s="29" t="n"/>
       <c r="H31" s="57" t="n"/>
       <c r="I31" s="57" t="n"/>
       <c r="J31" s="57" t="n"/>
-      <c r="K31" s="25">
+      <c r="K31" s="28">
         <f>IFERROR(J31/I31,"")</f>
         <v/>
       </c>
       <c r="L31" s="57" t="n"/>
       <c r="M31" s="57" t="n"/>
-      <c r="N31" s="25">
+      <c r="N31" s="28">
         <f>IFERROR(M31/L31,"")</f>
         <v/>
       </c>
       <c r="O31" s="57" t="n"/>
       <c r="P31" s="57" t="n"/>
-      <c r="Q31" s="26" t="n"/>
+      <c r="Q31" s="29" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="70">
       <c r="A32" s="57" t="n">
         <v>13</v>
       </c>
-      <c r="B32" s="26" t="n"/>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="24" t="n"/>
-      <c r="F32" s="24" t="n"/>
-      <c r="G32" s="26" t="n"/>
+      <c r="B32" s="29" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="27" t="n"/>
+      <c r="F32" s="27" t="n"/>
+      <c r="G32" s="29" t="n"/>
       <c r="H32" s="57" t="n"/>
       <c r="I32" s="57" t="n"/>
       <c r="J32" s="57" t="n"/>
-      <c r="K32" s="25">
+      <c r="K32" s="28">
         <f>IFERROR(J32/I32,"")</f>
         <v/>
       </c>
       <c r="L32" s="57" t="n"/>
       <c r="M32" s="57" t="n"/>
-      <c r="N32" s="25">
+      <c r="N32" s="28">
         <f>IFERROR(M32/L32,"")</f>
         <v/>
       </c>
       <c r="O32" s="57" t="n"/>
       <c r="P32" s="57" t="n"/>
-      <c r="Q32" s="26" t="n"/>
+      <c r="Q32" s="29" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="70">
       <c r="A33" s="57" t="n">
         <v>14</v>
       </c>
-      <c r="B33" s="26" t="n"/>
-      <c r="C33" s="26" t="n"/>
-      <c r="D33" s="26" t="n"/>
-      <c r="E33" s="24" t="n"/>
-      <c r="F33" s="24" t="n"/>
-      <c r="G33" s="26" t="n"/>
+      <c r="B33" s="29" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="29" t="n"/>
+      <c r="E33" s="27" t="n"/>
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="29" t="n"/>
       <c r="H33" s="57" t="n"/>
       <c r="I33" s="57" t="n"/>
       <c r="J33" s="57" t="n"/>
-      <c r="K33" s="25">
+      <c r="K33" s="28">
         <f>IFERROR(J33/I33,"")</f>
         <v/>
       </c>
       <c r="L33" s="57" t="n"/>
       <c r="M33" s="57" t="n"/>
-      <c r="N33" s="25">
+      <c r="N33" s="28">
         <f>IFERROR(M33/L33,"")</f>
         <v/>
       </c>
       <c r="O33" s="57" t="n"/>
       <c r="P33" s="57" t="n"/>
-      <c r="Q33" s="26" t="n"/>
+      <c r="Q33" s="29" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="70">
       <c r="A34" s="57" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="26" t="n"/>
-      <c r="C34" s="26" t="n"/>
-      <c r="D34" s="26" t="n"/>
-      <c r="E34" s="24" t="n"/>
-      <c r="F34" s="24" t="n"/>
-      <c r="G34" s="26" t="n"/>
+      <c r="B34" s="29" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="29" t="n"/>
+      <c r="E34" s="27" t="n"/>
+      <c r="F34" s="27" t="n"/>
+      <c r="G34" s="29" t="n"/>
       <c r="H34" s="57" t="n"/>
       <c r="I34" s="57" t="n"/>
       <c r="J34" s="57" t="n"/>
-      <c r="K34" s="25">
+      <c r="K34" s="28">
         <f>IFERROR(J34/I34,"")</f>
         <v/>
       </c>
       <c r="L34" s="57" t="n"/>
       <c r="M34" s="57" t="n"/>
-      <c r="N34" s="25">
+      <c r="N34" s="28">
         <f>IFERROR(M34/L34,"")</f>
         <v/>
       </c>
       <c r="O34" s="57" t="n"/>
       <c r="P34" s="57" t="n"/>
-      <c r="Q34" s="26" t="n"/>
+      <c r="Q34" s="29" t="n"/>
     </row>
     <row r="35" ht="21" customHeight="1" s="70">
       <c r="A35" s="60" t="inlineStr">
@@ -2216,13 +2208,13 @@
           <t>TOTALES</t>
         </is>
       </c>
-      <c r="B35" s="27" t="n"/>
-      <c r="C35" s="27" t="n"/>
-      <c r="D35" s="27" t="n"/>
-      <c r="E35" s="27" t="n"/>
-      <c r="F35" s="27" t="n"/>
-      <c r="G35" s="27" t="n"/>
-      <c r="H35" s="28" t="n"/>
+      <c r="B35" s="30" t="n"/>
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="30" t="n"/>
+      <c r="E35" s="30" t="n"/>
+      <c r="F35" s="30" t="n"/>
+      <c r="G35" s="30" t="n"/>
+      <c r="H35" s="31" t="n"/>
       <c r="I35" s="58">
         <f>SUM(I20:I34)</f>
         <v/>
@@ -2231,7 +2223,7 @@
         <f>SUM(J20:J34)</f>
         <v/>
       </c>
-      <c r="K35" s="29">
+      <c r="K35" s="32">
         <f>IFERROR(J35/I35,"")</f>
         <v/>
       </c>
@@ -2243,223 +2235,223 @@
         <f>SUM(M20:M34)</f>
         <v/>
       </c>
-      <c r="N35" s="29">
+      <c r="N35" s="32">
         <f>IFERROR(M35/L35,"")</f>
         <v/>
       </c>
-      <c r="O35" s="39" t="n"/>
-      <c r="P35" s="27" t="n"/>
-      <c r="Q35" s="28" t="n"/>
+      <c r="O35" s="42" t="n"/>
+      <c r="P35" s="30" t="n"/>
+      <c r="Q35" s="31" t="n"/>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="70">
-      <c r="A36" s="51" t="inlineStr">
+      <c r="A36" s="54" t="inlineStr">
         <is>
           <t>4. OBSERVACIONES Y SEGUIMIENTO</t>
         </is>
       </c>
-      <c r="B36" s="35" t="n"/>
-      <c r="C36" s="35" t="n"/>
-      <c r="D36" s="35" t="n"/>
-      <c r="E36" s="35" t="n"/>
-      <c r="F36" s="35" t="n"/>
-      <c r="G36" s="35" t="n"/>
-      <c r="H36" s="35" t="n"/>
-      <c r="I36" s="35" t="n"/>
-      <c r="J36" s="35" t="n"/>
-      <c r="K36" s="35" t="n"/>
-      <c r="L36" s="35" t="n"/>
-      <c r="M36" s="35" t="n"/>
-      <c r="N36" s="35" t="n"/>
-      <c r="O36" s="35" t="n"/>
-      <c r="P36" s="35" t="n"/>
-      <c r="Q36" s="44" t="n"/>
+      <c r="B36" s="38" t="n"/>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="38" t="n"/>
+      <c r="E36" s="38" t="n"/>
+      <c r="F36" s="38" t="n"/>
+      <c r="G36" s="38" t="n"/>
+      <c r="H36" s="38" t="n"/>
+      <c r="I36" s="38" t="n"/>
+      <c r="J36" s="38" t="n"/>
+      <c r="K36" s="38" t="n"/>
+      <c r="L36" s="38" t="n"/>
+      <c r="M36" s="38" t="n"/>
+      <c r="N36" s="38" t="n"/>
+      <c r="O36" s="38" t="n"/>
+      <c r="P36" s="38" t="n"/>
+      <c r="Q36" s="47" t="n"/>
     </row>
     <row r="37" ht="19.95" customHeight="1" s="70">
-      <c r="A37" s="49" t="n"/>
-      <c r="B37" s="53" t="n"/>
-      <c r="C37" s="53" t="n"/>
-      <c r="D37" s="53" t="n"/>
-      <c r="E37" s="53" t="n"/>
-      <c r="F37" s="53" t="n"/>
-      <c r="G37" s="53" t="n"/>
-      <c r="H37" s="53" t="n"/>
-      <c r="I37" s="53" t="n"/>
-      <c r="J37" s="53" t="n"/>
-      <c r="K37" s="53" t="n"/>
-      <c r="L37" s="53" t="n"/>
-      <c r="M37" s="53" t="n"/>
-      <c r="N37" s="53" t="n"/>
-      <c r="O37" s="53" t="n"/>
-      <c r="P37" s="53" t="n"/>
-      <c r="Q37" s="42" t="n"/>
+      <c r="A37" s="52" t="n"/>
+      <c r="B37" s="56" t="n"/>
+      <c r="C37" s="56" t="n"/>
+      <c r="D37" s="56" t="n"/>
+      <c r="E37" s="56" t="n"/>
+      <c r="F37" s="56" t="n"/>
+      <c r="G37" s="56" t="n"/>
+      <c r="H37" s="56" t="n"/>
+      <c r="I37" s="56" t="n"/>
+      <c r="J37" s="56" t="n"/>
+      <c r="K37" s="56" t="n"/>
+      <c r="L37" s="56" t="n"/>
+      <c r="M37" s="56" t="n"/>
+      <c r="N37" s="56" t="n"/>
+      <c r="O37" s="56" t="n"/>
+      <c r="P37" s="56" t="n"/>
+      <c r="Q37" s="45" t="n"/>
     </row>
     <row r="38" ht="19.95" customHeight="1" s="70">
-      <c r="A38" s="34" t="n"/>
-      <c r="B38" s="35" t="n"/>
-      <c r="C38" s="35" t="n"/>
-      <c r="D38" s="35" t="n"/>
-      <c r="E38" s="35" t="n"/>
-      <c r="F38" s="35" t="n"/>
-      <c r="G38" s="35" t="n"/>
-      <c r="H38" s="35" t="n"/>
-      <c r="I38" s="35" t="n"/>
-      <c r="J38" s="35" t="n"/>
-      <c r="K38" s="35" t="n"/>
-      <c r="L38" s="35" t="n"/>
-      <c r="M38" s="35" t="n"/>
-      <c r="N38" s="35" t="n"/>
-      <c r="O38" s="35" t="n"/>
-      <c r="P38" s="35" t="n"/>
-      <c r="Q38" s="44" t="n"/>
+      <c r="A38" s="37" t="n"/>
+      <c r="B38" s="38" t="n"/>
+      <c r="C38" s="38" t="n"/>
+      <c r="D38" s="38" t="n"/>
+      <c r="E38" s="38" t="n"/>
+      <c r="F38" s="38" t="n"/>
+      <c r="G38" s="38" t="n"/>
+      <c r="H38" s="38" t="n"/>
+      <c r="I38" s="38" t="n"/>
+      <c r="J38" s="38" t="n"/>
+      <c r="K38" s="38" t="n"/>
+      <c r="L38" s="38" t="n"/>
+      <c r="M38" s="38" t="n"/>
+      <c r="N38" s="38" t="n"/>
+      <c r="O38" s="38" t="n"/>
+      <c r="P38" s="38" t="n"/>
+      <c r="Q38" s="47" t="n"/>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="70">
-      <c r="A39" s="51" t="inlineStr">
+      <c r="A39" s="54" t="inlineStr">
         <is>
           <t>5. FIRMAS</t>
         </is>
       </c>
-      <c r="B39" s="35" t="n"/>
-      <c r="C39" s="35" t="n"/>
-      <c r="D39" s="35" t="n"/>
-      <c r="E39" s="35" t="n"/>
-      <c r="F39" s="35" t="n"/>
-      <c r="G39" s="35" t="n"/>
-      <c r="H39" s="35" t="n"/>
-      <c r="I39" s="35" t="n"/>
-      <c r="J39" s="35" t="n"/>
-      <c r="K39" s="35" t="n"/>
-      <c r="L39" s="35" t="n"/>
-      <c r="M39" s="35" t="n"/>
-      <c r="N39" s="35" t="n"/>
-      <c r="O39" s="35" t="n"/>
-      <c r="P39" s="35" t="n"/>
-      <c r="Q39" s="44" t="n"/>
+      <c r="B39" s="38" t="n"/>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="38" t="n"/>
+      <c r="E39" s="38" t="n"/>
+      <c r="F39" s="38" t="n"/>
+      <c r="G39" s="38" t="n"/>
+      <c r="H39" s="38" t="n"/>
+      <c r="I39" s="38" t="n"/>
+      <c r="J39" s="38" t="n"/>
+      <c r="K39" s="38" t="n"/>
+      <c r="L39" s="38" t="n"/>
+      <c r="M39" s="38" t="n"/>
+      <c r="N39" s="38" t="n"/>
+      <c r="O39" s="38" t="n"/>
+      <c r="P39" s="38" t="n"/>
+      <c r="Q39" s="47" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1" s="70">
-      <c r="A40" s="48" t="inlineStr">
+      <c r="A40" s="51" t="inlineStr">
         <is>
           <t>ELABORÓ — RESPONSABLE SST</t>
         </is>
       </c>
-      <c r="B40" s="27" t="n"/>
-      <c r="C40" s="27" t="n"/>
-      <c r="D40" s="27" t="n"/>
-      <c r="E40" s="27" t="n"/>
-      <c r="F40" s="27" t="n"/>
-      <c r="G40" s="28" t="n"/>
-      <c r="H40" s="48" t="inlineStr">
+      <c r="B40" s="30" t="n"/>
+      <c r="C40" s="30" t="n"/>
+      <c r="D40" s="30" t="n"/>
+      <c r="E40" s="30" t="n"/>
+      <c r="F40" s="30" t="n"/>
+      <c r="G40" s="31" t="n"/>
+      <c r="H40" s="51" t="inlineStr">
         <is>
           <t>REVISÓ — RESIDENTE / DIRECTOR DE OBRA</t>
         </is>
       </c>
-      <c r="I40" s="27" t="n"/>
-      <c r="J40" s="27" t="n"/>
-      <c r="K40" s="27" t="n"/>
-      <c r="L40" s="27" t="n"/>
-      <c r="M40" s="27" t="n"/>
-      <c r="N40" s="28" t="n"/>
-      <c r="O40" s="48" t="inlineStr">
+      <c r="I40" s="30" t="n"/>
+      <c r="J40" s="30" t="n"/>
+      <c r="K40" s="30" t="n"/>
+      <c r="L40" s="30" t="n"/>
+      <c r="M40" s="30" t="n"/>
+      <c r="N40" s="31" t="n"/>
+      <c r="O40" s="51" t="inlineStr">
         <is>
           <t>Vo.Bo. GERENCIA</t>
         </is>
       </c>
-      <c r="P40" s="27" t="n"/>
-      <c r="Q40" s="28" t="n"/>
+      <c r="P40" s="30" t="n"/>
+      <c r="Q40" s="31" t="n"/>
     </row>
     <row r="41" ht="42" customHeight="1" s="70">
-      <c r="A41" s="36" t="inlineStr">
+      <c r="A41" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="B41" s="28" t="n"/>
-      <c r="C41" s="40" t="n"/>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="27" t="n"/>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="28" t="n"/>
-      <c r="H41" s="36" t="inlineStr">
+      <c r="B41" s="31" t="n"/>
+      <c r="C41" s="43" t="n"/>
+      <c r="D41" s="30" t="n"/>
+      <c r="E41" s="30" t="n"/>
+      <c r="F41" s="30" t="n"/>
+      <c r="G41" s="31" t="n"/>
+      <c r="H41" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="I41" s="28" t="n"/>
-      <c r="J41" s="40" t="n"/>
-      <c r="K41" s="27" t="n"/>
-      <c r="L41" s="27" t="n"/>
-      <c r="M41" s="27" t="n"/>
-      <c r="N41" s="28" t="n"/>
-      <c r="O41" s="36" t="inlineStr">
+      <c r="I41" s="31" t="n"/>
+      <c r="J41" s="43" t="n"/>
+      <c r="K41" s="30" t="n"/>
+      <c r="L41" s="30" t="n"/>
+      <c r="M41" s="30" t="n"/>
+      <c r="N41" s="31" t="n"/>
+      <c r="O41" s="39" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="P41" s="28" t="n"/>
-      <c r="Q41" s="40" t="n"/>
+      <c r="P41" s="31" t="n"/>
+      <c r="Q41" s="43" t="n"/>
     </row>
     <row r="42" ht="21" customHeight="1" s="70">
-      <c r="A42" s="36" t="inlineStr">
+      <c r="A42" s="39" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="B42" s="28" t="n"/>
-      <c r="C42" s="40" t="n"/>
-      <c r="D42" s="27" t="n"/>
-      <c r="E42" s="27" t="n"/>
-      <c r="F42" s="27" t="n"/>
-      <c r="G42" s="28" t="n"/>
-      <c r="H42" s="36" t="inlineStr">
+      <c r="B42" s="31" t="n"/>
+      <c r="C42" s="43" t="n"/>
+      <c r="D42" s="30" t="n"/>
+      <c r="E42" s="30" t="n"/>
+      <c r="F42" s="30" t="n"/>
+      <c r="G42" s="31" t="n"/>
+      <c r="H42" s="39" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="I42" s="28" t="n"/>
-      <c r="J42" s="40" t="n"/>
-      <c r="K42" s="27" t="n"/>
-      <c r="L42" s="27" t="n"/>
-      <c r="M42" s="27" t="n"/>
-      <c r="N42" s="28" t="n"/>
-      <c r="O42" s="36" t="inlineStr">
+      <c r="I42" s="31" t="n"/>
+      <c r="J42" s="43" t="n"/>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="30" t="n"/>
+      <c r="M42" s="30" t="n"/>
+      <c r="N42" s="31" t="n"/>
+      <c r="O42" s="39" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="P42" s="28" t="n"/>
-      <c r="Q42" s="40" t="n"/>
+      <c r="P42" s="31" t="n"/>
+      <c r="Q42" s="43" t="n"/>
     </row>
     <row r="43" ht="21" customHeight="1" s="70">
-      <c r="A43" s="36" t="inlineStr">
+      <c r="A43" s="39" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="B43" s="28" t="n"/>
-      <c r="C43" s="40" t="n"/>
-      <c r="D43" s="27" t="n"/>
-      <c r="E43" s="27" t="n"/>
-      <c r="F43" s="27" t="n"/>
-      <c r="G43" s="28" t="n"/>
-      <c r="H43" s="36" t="inlineStr">
+      <c r="B43" s="31" t="n"/>
+      <c r="C43" s="43" t="n"/>
+      <c r="D43" s="30" t="n"/>
+      <c r="E43" s="30" t="n"/>
+      <c r="F43" s="30" t="n"/>
+      <c r="G43" s="31" t="n"/>
+      <c r="H43" s="39" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="I43" s="28" t="n"/>
-      <c r="J43" s="40" t="n"/>
-      <c r="K43" s="27" t="n"/>
-      <c r="L43" s="27" t="n"/>
-      <c r="M43" s="27" t="n"/>
-      <c r="N43" s="28" t="n"/>
-      <c r="O43" s="36" t="inlineStr">
+      <c r="I43" s="31" t="n"/>
+      <c r="J43" s="43" t="n"/>
+      <c r="K43" s="30" t="n"/>
+      <c r="L43" s="30" t="n"/>
+      <c r="M43" s="30" t="n"/>
+      <c r="N43" s="31" t="n"/>
+      <c r="O43" s="39" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="P43" s="28" t="n"/>
-      <c r="Q43" s="40" t="n"/>
-    </row>
-    <row r="44" customFormat="1" s="64">
+      <c r="P43" s="31" t="n"/>
+      <c r="Q43" s="43" t="n"/>
+    </row>
+    <row r="44" s="64">
       <c r="A44" s="61" t="inlineStr">
         <is>
           <t>REV. 04/10/2026</t>
@@ -2542,7 +2534,7 @@
     <mergeCell ref="P5:Q5"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.7" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0"/>
+  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;8 Página &amp;P de &amp;N</oddFooter>

--- a/public/plantilla-capacitaciones.xlsx
+++ b/public/plantilla-capacitaciones.xlsx
@@ -3,19 +3,19 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacitaciones" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="27">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,14 +75,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <family val="2"/>
       <b val="1"/>
@@ -165,14 +157,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <sz val="9.5"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="0"/>
-      <sz val="8.5"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -212,19 +196,114 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <sz val="7"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF404040"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF1B2A45"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="8.5"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF0B1F33"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -236,18 +315,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
-        <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
     <fill>
@@ -270,24 +337,84 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F75B5"/>
+        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1F33"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B1F33"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE5A018"/>
+        <bgColor rgb="FFEEF1F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF3"/>
         <bgColor rgb="FFEEF1F6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.0499893185216834"/>
-        <bgColor rgb="FF003366"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFCCF6A"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -414,19 +541,6 @@
         <color rgb="FF9AA3B2"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </top>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -526,26 +640,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="3" tint="0.5999633777886288"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="0"/>
       </left>
@@ -570,6 +664,327 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9AA3B2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0B1F33"/>
+      </left>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF0B1F33"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.5999633777886288"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0B1F33"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -585,6 +1000,17 @@
       </right>
       <top style="thin">
         <color theme="3" tint="0.5999633777886288"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF9AA3B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0B1F33"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -598,298 +1024,911 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="30" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="15" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="12" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="33" fillId="16" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -899,7 +1938,154 @@
     <cellStyle name="Normal 4" xfId="4"/>
     <cellStyle name="Normal 6 2" xfId="5"/>
   </cellStyles>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00A651"/>
+          <bgColor rgb="FF00A651"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF595959"/>
+          <bgColor rgb="FF595959"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7F4F24"/>
+          <bgColor rgb="FF7F4F24"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF7030A0"/>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF57C00"/>
+          <bgColor rgb="FFF57C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF00A651"/>
+          <bgColor rgb="FF00A651"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF000000"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC000"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0070C0"/>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC00000"/>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -913,10 +2099,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>2247900</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>131445</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>810532</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>177646</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -930,6 +2116,10 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="0" y="0"/>
+          <a:ext cx="3492000" cy="1692000"/>
+        </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
@@ -1247,1234 +2437,1219 @@
   <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col width="5" customWidth="1" style="70" min="1" max="1"/>
-    <col width="34" customWidth="1" style="70" min="2" max="2"/>
-    <col width="16" customWidth="1" style="70" min="3" max="4"/>
-    <col width="11" customWidth="1" style="70" min="5" max="6"/>
-    <col width="18" customWidth="1" style="70" min="7" max="7"/>
-    <col width="9" customWidth="1" style="70" min="8" max="8"/>
-    <col width="9.44140625" customWidth="1" style="70" min="9" max="10"/>
-    <col width="10" customWidth="1" style="70" min="11" max="11"/>
-    <col width="9.44140625" customWidth="1" style="70" min="12" max="13"/>
-    <col width="10" customWidth="1" style="70" min="14" max="14"/>
-    <col width="16" customWidth="1" style="70" min="15" max="15"/>
-    <col width="13" customWidth="1" style="70" min="16" max="16"/>
-    <col width="22" customWidth="1" style="70" min="17" max="17"/>
+    <col width="5" customWidth="1" style="127" min="1" max="1"/>
+    <col width="34" customWidth="1" style="127" min="2" max="2"/>
+    <col width="16" customWidth="1" style="127" min="3" max="4"/>
+    <col width="11" customWidth="1" style="127" min="5" max="6"/>
+    <col width="18" customWidth="1" style="127" min="7" max="7"/>
+    <col width="9" customWidth="1" style="127" min="8" max="8"/>
+    <col width="9.44140625" customWidth="1" style="127" min="9" max="10"/>
+    <col width="10" customWidth="1" style="127" min="11" max="11"/>
+    <col width="9.44140625" customWidth="1" style="127" min="12" max="13"/>
+    <col width="10" customWidth="1" style="127" min="14" max="14"/>
+    <col width="16" customWidth="1" style="127" min="15" max="15"/>
+    <col width="13" customWidth="1" style="127" min="16" max="16"/>
+    <col width="22" customWidth="1" style="127" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40.05" customHeight="1" s="70">
-      <c r="D1" s="35" t="inlineStr">
+    <row r="1" ht="40.05" customHeight="1" s="127">
+      <c r="D1" s="133" t="inlineStr">
         <is>
           <t>MATRIZ DE CAPACITACIÓN SG-SST</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="14.4" customHeight="1" s="70">
-      <c r="D2" s="37" t="n"/>
-      <c r="E2" s="38" t="n"/>
-      <c r="F2" s="38" t="n"/>
-      <c r="G2" s="38" t="n"/>
-      <c r="H2" s="38" t="n"/>
-      <c r="I2" s="38" t="n"/>
-      <c r="J2" s="38" t="n"/>
-      <c r="K2" s="38" t="n"/>
-      <c r="L2" s="38" t="n"/>
-      <c r="M2" s="38" t="n"/>
-      <c r="N2" s="38" t="n"/>
-      <c r="O2" s="38" t="n"/>
-      <c r="P2" s="38" t="n"/>
-      <c r="Q2" s="38" t="n"/>
-    </row>
-    <row r="3" ht="4.95" customHeight="1" s="70">
-      <c r="D3" s="67" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="30" t="n"/>
-      <c r="O3" s="30" t="n"/>
-      <c r="P3" s="30" t="n"/>
-      <c r="Q3" s="31" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="70">
-      <c r="O4" s="53" t="inlineStr">
+    <row r="2" ht="14.4" customHeight="1" s="127">
+      <c r="D2" s="96" t="n"/>
+      <c r="E2" s="98" t="n"/>
+      <c r="F2" s="98" t="n"/>
+      <c r="G2" s="98" t="n"/>
+      <c r="H2" s="98" t="n"/>
+      <c r="I2" s="98" t="n"/>
+      <c r="J2" s="98" t="n"/>
+      <c r="K2" s="98" t="n"/>
+      <c r="L2" s="98" t="n"/>
+      <c r="M2" s="98" t="n"/>
+      <c r="N2" s="98" t="n"/>
+      <c r="O2" s="98" t="n"/>
+      <c r="P2" s="98" t="n"/>
+      <c r="Q2" s="98" t="n"/>
+    </row>
+    <row r="3" ht="4.95" customHeight="1" s="127">
+      <c r="D3" s="101" t="n"/>
+      <c r="E3" s="93" t="n"/>
+      <c r="F3" s="93" t="n"/>
+      <c r="G3" s="93" t="n"/>
+      <c r="H3" s="93" t="n"/>
+      <c r="I3" s="93" t="n"/>
+      <c r="J3" s="93" t="n"/>
+      <c r="K3" s="93" t="n"/>
+      <c r="L3" s="93" t="n"/>
+      <c r="M3" s="93" t="n"/>
+      <c r="N3" s="93" t="n"/>
+      <c r="O3" s="93" t="n"/>
+      <c r="P3" s="93" t="n"/>
+      <c r="Q3" s="89" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="127">
+      <c r="O4" s="139" t="inlineStr">
         <is>
           <t>CONTROL DOCUMENTAL</t>
         </is>
       </c>
-      <c r="P4" s="30" t="n"/>
-      <c r="Q4" s="31" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="70">
-      <c r="D5" s="40" t="inlineStr">
+      <c r="P4" s="93" t="n"/>
+      <c r="Q4" s="89" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="127">
+      <c r="D5" s="99" t="inlineStr">
         <is>
           <t>REFORMAS Y REMODELACIONES</t>
         </is>
       </c>
-      <c r="N5" s="41" t="n"/>
+      <c r="N5" s="92" t="n"/>
       <c r="O5" s="5" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="P5" s="49" t="inlineStr">
+      <c r="P5" s="64" t="inlineStr">
         <is>
           <t>RYR-SS-005</t>
         </is>
       </c>
-      <c r="Q5" s="31" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="70">
-      <c r="D6" s="44" t="inlineStr">
+      <c r="Q5" s="89" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="127">
+      <c r="D6" s="90" t="inlineStr">
         <is>
           <t>DISEÑAMOS, RENOVAMOS Y CONSTRUIMOS ESPACIOS QUE INSPIRAN.</t>
         </is>
       </c>
-      <c r="N6" s="41" t="n"/>
+      <c r="N6" s="92" t="n"/>
       <c r="O6" s="5" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="P6" s="49" t="n">
+      <c r="P6" s="64" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" s="31" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="70">
-      <c r="D7" s="79" t="n"/>
-      <c r="E7" s="80" t="n"/>
-      <c r="F7" s="80" t="n"/>
-      <c r="G7" s="80" t="n"/>
-      <c r="H7" s="80" t="n"/>
-      <c r="I7" s="80" t="n"/>
-      <c r="J7" s="80" t="n"/>
-      <c r="K7" s="80" t="n"/>
-      <c r="L7" s="80" t="n"/>
-      <c r="M7" s="80" t="n"/>
-      <c r="N7" s="81" t="n"/>
+      <c r="Q6" s="89" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="127">
+      <c r="D7" s="65" t="n"/>
+      <c r="E7" s="190" t="n"/>
+      <c r="F7" s="190" t="n"/>
+      <c r="G7" s="190" t="n"/>
+      <c r="H7" s="190" t="n"/>
+      <c r="I7" s="190" t="n"/>
+      <c r="J7" s="190" t="n"/>
+      <c r="K7" s="190" t="n"/>
+      <c r="L7" s="190" t="n"/>
+      <c r="M7" s="190" t="n"/>
+      <c r="N7" s="67" t="n"/>
       <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Fecha de Emisión</t>
         </is>
       </c>
-      <c r="P7" s="49" t="inlineStr">
+      <c r="P7" s="64" t="inlineStr">
         <is>
           <t>04/10/2026</t>
         </is>
       </c>
-      <c r="Q7" s="31" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="70">
-      <c r="D8" s="71" t="n"/>
-      <c r="E8" s="66" t="n"/>
-      <c r="F8" s="66" t="n"/>
-      <c r="G8" s="66" t="n"/>
-      <c r="H8" s="66" t="n"/>
-      <c r="I8" s="66" t="n"/>
-      <c r="J8" s="66" t="n"/>
-      <c r="K8" s="66" t="n"/>
-      <c r="L8" s="66" t="n"/>
-      <c r="M8" s="66" t="n"/>
-      <c r="N8" s="81" t="n"/>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="Q7" s="89" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="127">
+      <c r="D8" s="65" t="n"/>
+      <c r="E8" s="190" t="n"/>
+      <c r="F8" s="190" t="n"/>
+      <c r="G8" s="190" t="n"/>
+      <c r="H8" s="190" t="n"/>
+      <c r="I8" s="190" t="n"/>
+      <c r="J8" s="190" t="n"/>
+      <c r="K8" s="190" t="n"/>
+      <c r="L8" s="190" t="n"/>
+      <c r="M8" s="190" t="n"/>
+      <c r="N8" s="67" t="n"/>
+      <c r="O8" s="254" t="inlineStr">
         <is>
           <t>Página</t>
         </is>
       </c>
-      <c r="P8" s="49" t="inlineStr">
+      <c r="P8" s="58" t="inlineStr">
         <is>
           <t>1 de 1</t>
         </is>
       </c>
-      <c r="Q8" s="31" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="70">
-      <c r="A9" s="103" t="inlineStr">
+      <c r="Q8" s="94" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="127">
+      <c r="A9" s="287" t="inlineStr">
         <is>
           <t>Programa de capacitación del proyecto: programación, ejecución, cobertura y eficacia · Decreto 1072 de 2015 · Resolución 0312 de 2019</t>
         </is>
       </c>
-      <c r="B9" s="115" t="n"/>
-      <c r="C9" s="115" t="n"/>
-      <c r="D9" s="115" t="n"/>
-      <c r="E9" s="115" t="n"/>
-      <c r="F9" s="115" t="n"/>
-      <c r="G9" s="115" t="n"/>
-      <c r="H9" s="115" t="n"/>
-      <c r="I9" s="115" t="n"/>
-      <c r="J9" s="115" t="n"/>
-      <c r="K9" s="115" t="n"/>
-      <c r="L9" s="115" t="n"/>
-      <c r="M9" s="115" t="n"/>
-      <c r="N9" s="115" t="n"/>
-      <c r="O9" s="115" t="n"/>
-      <c r="P9" s="115" t="n"/>
-      <c r="Q9" s="116" t="n"/>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" s="70">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="B9" s="347" t="n"/>
+      <c r="C9" s="347" t="n"/>
+      <c r="D9" s="347" t="n"/>
+      <c r="E9" s="347" t="n"/>
+      <c r="F9" s="347" t="n"/>
+      <c r="G9" s="347" t="n"/>
+      <c r="H9" s="347" t="n"/>
+      <c r="I9" s="347" t="n"/>
+      <c r="J9" s="347" t="n"/>
+      <c r="K9" s="347" t="n"/>
+      <c r="L9" s="347" t="n"/>
+      <c r="M9" s="347" t="n"/>
+      <c r="N9" s="347" t="n"/>
+      <c r="O9" s="347" t="n"/>
+      <c r="P9" s="347" t="n"/>
+      <c r="Q9" s="352" t="n"/>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" s="127">
+      <c r="A10" s="137" t="inlineStr">
         <is>
           <t>1. DATOS DEL PROGRAMA</t>
         </is>
       </c>
-      <c r="B10" s="38" t="n"/>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="38" t="n"/>
-      <c r="F10" s="38" t="n"/>
-      <c r="G10" s="38" t="n"/>
-      <c r="H10" s="38" t="n"/>
-      <c r="I10" s="38" t="n"/>
-      <c r="J10" s="38" t="n"/>
-      <c r="K10" s="38" t="n"/>
-      <c r="L10" s="38" t="n"/>
-      <c r="M10" s="38" t="n"/>
-      <c r="N10" s="38" t="n"/>
-      <c r="O10" s="38" t="n"/>
-      <c r="P10" s="38" t="n"/>
-      <c r="Q10" s="47" t="n"/>
-    </row>
-    <row r="11" ht="19.95" customHeight="1" s="70">
-      <c r="A11" s="33" t="inlineStr">
+      <c r="B10" s="98" t="n"/>
+      <c r="C10" s="98" t="n"/>
+      <c r="D10" s="98" t="n"/>
+      <c r="E10" s="98" t="n"/>
+      <c r="F10" s="98" t="n"/>
+      <c r="G10" s="98" t="n"/>
+      <c r="H10" s="98" t="n"/>
+      <c r="I10" s="98" t="n"/>
+      <c r="J10" s="98" t="n"/>
+      <c r="K10" s="98" t="n"/>
+      <c r="L10" s="98" t="n"/>
+      <c r="M10" s="98" t="n"/>
+      <c r="N10" s="98" t="n"/>
+      <c r="O10" s="98" t="n"/>
+      <c r="P10" s="98" t="n"/>
+      <c r="Q10" s="97" t="n"/>
+    </row>
+    <row r="11" ht="19.95" customHeight="1" s="127">
+      <c r="A11" s="59" t="inlineStr">
         <is>
           <t>Proyecto / Obra</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="50" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="31" t="n"/>
-      <c r="H11" s="33" t="inlineStr">
+      <c r="B11" s="89" t="n"/>
+      <c r="C11" s="161" t="n"/>
+      <c r="D11" s="93" t="n"/>
+      <c r="E11" s="93" t="n"/>
+      <c r="F11" s="93" t="n"/>
+      <c r="G11" s="89" t="n"/>
+      <c r="H11" s="59" t="inlineStr">
         <is>
           <t>Contratista / Empresa</t>
         </is>
       </c>
-      <c r="I11" s="30" t="n"/>
-      <c r="J11" s="30" t="n"/>
-      <c r="K11" s="31" t="n"/>
-      <c r="L11" s="43" t="n"/>
-      <c r="M11" s="30" t="n"/>
-      <c r="N11" s="30" t="n"/>
-      <c r="O11" s="30" t="n"/>
-      <c r="P11" s="30" t="n"/>
-      <c r="Q11" s="31" t="n"/>
-    </row>
-    <row r="12" ht="19.95" customHeight="1" s="70">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="I11" s="93" t="n"/>
+      <c r="J11" s="93" t="n"/>
+      <c r="K11" s="89" t="n"/>
+      <c r="L11" s="68" t="n"/>
+      <c r="M11" s="93" t="n"/>
+      <c r="N11" s="93" t="n"/>
+      <c r="O11" s="93" t="n"/>
+      <c r="P11" s="93" t="n"/>
+      <c r="Q11" s="89" t="n"/>
+    </row>
+    <row r="12" ht="19.95" customHeight="1" s="127">
+      <c r="A12" s="59" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
-      <c r="B12" s="31" t="n"/>
-      <c r="C12" s="43" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="31" t="n"/>
-      <c r="H12" s="33" t="inlineStr">
+      <c r="B12" s="89" t="n"/>
+      <c r="C12" s="68" t="n"/>
+      <c r="D12" s="93" t="n"/>
+      <c r="E12" s="93" t="n"/>
+      <c r="F12" s="93" t="n"/>
+      <c r="G12" s="89" t="n"/>
+      <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Responsable del programa SST</t>
         </is>
       </c>
-      <c r="I12" s="30" t="n"/>
-      <c r="J12" s="30" t="n"/>
-      <c r="K12" s="31" t="n"/>
-      <c r="L12" s="43" t="n"/>
-      <c r="M12" s="30" t="n"/>
-      <c r="N12" s="31" t="n"/>
-      <c r="O12" s="33" t="inlineStr">
+      <c r="I12" s="93" t="n"/>
+      <c r="J12" s="93" t="n"/>
+      <c r="K12" s="89" t="n"/>
+      <c r="L12" s="68" t="n"/>
+      <c r="M12" s="93" t="n"/>
+      <c r="N12" s="89" t="n"/>
+      <c r="O12" s="59" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="P12" s="43" t="n"/>
-      <c r="Q12" s="31" t="n"/>
-    </row>
-    <row r="13" ht="19.95" customHeight="1" s="70">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="P12" s="68" t="n"/>
+      <c r="Q12" s="89" t="n"/>
+    </row>
+    <row r="13" ht="19.95" customHeight="1" s="127">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>Periodo evaluado — desde</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="48" t="n"/>
-      <c r="D13" s="33" t="inlineStr">
+      <c r="B13" s="89" t="n"/>
+      <c r="C13" s="69" t="n"/>
+      <c r="D13" s="59" t="inlineStr">
         <is>
           <t>hasta</t>
         </is>
       </c>
-      <c r="E13" s="48" t="n"/>
-      <c r="F13" s="30" t="n"/>
-      <c r="G13" s="31" t="n"/>
-      <c r="H13" s="33" t="inlineStr">
+      <c r="E13" s="69" t="n"/>
+      <c r="F13" s="93" t="n"/>
+      <c r="G13" s="89" t="n"/>
+      <c r="H13" s="59" t="inlineStr">
         <is>
           <t>Fecha de actualización</t>
         </is>
       </c>
-      <c r="I13" s="30" t="n"/>
-      <c r="J13" s="30" t="n"/>
-      <c r="K13" s="31" t="n"/>
-      <c r="L13" s="48" t="n"/>
-      <c r="M13" s="30" t="n"/>
-      <c r="N13" s="31" t="n"/>
-      <c r="Q13" s="45" t="n"/>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" s="70">
-      <c r="A14" s="54" t="inlineStr">
+      <c r="I13" s="93" t="n"/>
+      <c r="J13" s="93" t="n"/>
+      <c r="K13" s="89" t="n"/>
+      <c r="L13" s="69" t="n"/>
+      <c r="M13" s="93" t="n"/>
+      <c r="N13" s="89" t="n"/>
+      <c r="Q13" s="94" t="n"/>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" s="127">
+      <c r="A14" s="137" t="inlineStr">
         <is>
           <t>2. INDICADORES DEL PROGRAMA (se calculan solos con la matriz)</t>
         </is>
       </c>
-      <c r="B14" s="38" t="n"/>
-      <c r="C14" s="38" t="n"/>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="38" t="n"/>
-      <c r="F14" s="38" t="n"/>
-      <c r="G14" s="38" t="n"/>
-      <c r="H14" s="38" t="n"/>
-      <c r="I14" s="38" t="n"/>
-      <c r="J14" s="38" t="n"/>
-      <c r="K14" s="38" t="n"/>
-      <c r="L14" s="38" t="n"/>
-      <c r="M14" s="38" t="n"/>
-      <c r="N14" s="38" t="n"/>
-      <c r="O14" s="38" t="n"/>
-      <c r="P14" s="38" t="n"/>
-      <c r="Q14" s="47" t="n"/>
-    </row>
-    <row r="15" ht="27" customHeight="1" s="70">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="B14" s="98" t="n"/>
+      <c r="C14" s="98" t="n"/>
+      <c r="D14" s="98" t="n"/>
+      <c r="E14" s="98" t="n"/>
+      <c r="F14" s="98" t="n"/>
+      <c r="G14" s="98" t="n"/>
+      <c r="H14" s="98" t="n"/>
+      <c r="I14" s="98" t="n"/>
+      <c r="J14" s="98" t="n"/>
+      <c r="K14" s="98" t="n"/>
+      <c r="L14" s="98" t="n"/>
+      <c r="M14" s="98" t="n"/>
+      <c r="N14" s="98" t="n"/>
+      <c r="O14" s="98" t="n"/>
+      <c r="P14" s="98" t="n"/>
+      <c r="Q14" s="97" t="n"/>
+    </row>
+    <row r="15" ht="27" customHeight="1" s="127">
+      <c r="A15" s="324" t="inlineStr">
         <is>
           <t>Capacitaciones programadas</t>
         </is>
       </c>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="B15" s="94" t="n"/>
+      <c r="C15" s="324" t="inlineStr">
         <is>
           <t>Capacitaciones ejecutadas</t>
         </is>
       </c>
-      <c r="D15" s="31" t="n"/>
-      <c r="E15" s="34" t="inlineStr">
+      <c r="D15" s="94" t="n"/>
+      <c r="E15" s="324" t="inlineStr">
         <is>
           <t>% de cumplimiento</t>
         </is>
       </c>
-      <c r="F15" s="31" t="n"/>
-      <c r="G15" s="34" t="inlineStr">
+      <c r="F15" s="94" t="n"/>
+      <c r="G15" s="74" t="inlineStr">
         <is>
           <t>Meta de cumplimiento</t>
         </is>
       </c>
-      <c r="H15" s="34" t="inlineStr">
+      <c r="H15" s="324" t="inlineStr">
         <is>
           <t>Personas convocadas</t>
         </is>
       </c>
-      <c r="I15" s="31" t="n"/>
-      <c r="J15" s="34" t="inlineStr">
+      <c r="I15" s="94" t="n"/>
+      <c r="J15" s="324" t="inlineStr">
         <is>
           <t>Personas asistentes</t>
         </is>
       </c>
-      <c r="K15" s="31" t="n"/>
-      <c r="L15" s="34" t="inlineStr">
+      <c r="K15" s="94" t="n"/>
+      <c r="L15" s="324" t="inlineStr">
         <is>
           <t>Cobertura global</t>
         </is>
       </c>
-      <c r="M15" s="31" t="n"/>
-      <c r="N15" s="34" t="inlineStr">
+      <c r="M15" s="94" t="n"/>
+      <c r="N15" s="74" t="inlineStr">
         <is>
           <t>Meta de cobertura</t>
         </is>
       </c>
-      <c r="O15" s="31" t="n"/>
-      <c r="P15" s="34" t="inlineStr">
+      <c r="O15" s="89" t="n"/>
+      <c r="P15" s="324" t="inlineStr">
         <is>
           <t>Eficacia global</t>
         </is>
       </c>
-      <c r="Q15" s="34" t="inlineStr">
+      <c r="Q15" s="74" t="inlineStr">
         <is>
           <t>Meta de eficacia</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="21" customHeight="1" s="70">
-      <c r="A16" s="58">
+    <row r="16" ht="21" customHeight="1" s="127">
+      <c r="A16" s="320">
         <f>COUNTA(B20:B34)</f>
         <v/>
       </c>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="58">
+      <c r="B16" s="348" t="n"/>
+      <c r="C16" s="320">
         <f>COUNTIF(P20:P34,"Ejecutada")</f>
         <v/>
       </c>
-      <c r="D16" s="31" t="n"/>
-      <c r="E16" s="32">
+      <c r="D16" s="348" t="n"/>
+      <c r="E16" s="321">
         <f>IFERROR(C16/A16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="31" t="n"/>
-      <c r="G16" s="59" t="n">
+      <c r="F16" s="348" t="n"/>
+      <c r="G16" s="322" t="n">
         <v>0.9</v>
       </c>
-      <c r="H16" s="58">
+      <c r="H16" s="320">
         <f>SUM(I20:I34)</f>
         <v/>
       </c>
-      <c r="I16" s="31" t="n"/>
-      <c r="J16" s="58">
+      <c r="I16" s="348" t="n"/>
+      <c r="J16" s="320">
         <f>SUM(J20:J34)</f>
         <v/>
       </c>
-      <c r="K16" s="31" t="n"/>
-      <c r="L16" s="32">
+      <c r="K16" s="348" t="n"/>
+      <c r="L16" s="321">
         <f>IFERROR(J16/H16,"")</f>
         <v/>
       </c>
-      <c r="M16" s="31" t="n"/>
-      <c r="N16" s="59" t="n">
+      <c r="M16" s="348" t="n"/>
+      <c r="N16" s="323" t="n">
         <v>0.8</v>
       </c>
-      <c r="O16" s="31" t="n"/>
-      <c r="P16" s="32">
+      <c r="O16" s="89" t="n"/>
+      <c r="P16" s="325">
         <f>IFERROR(SUM(M20:M34)/SUM(L20:L34),"")</f>
         <v/>
       </c>
-      <c r="Q16" s="59" t="n">
+      <c r="Q16" s="323" t="n">
         <v>0.8</v>
       </c>
     </row>
-    <row r="17" ht="19.95" customHeight="1" s="70">
-      <c r="A17" s="33" t="inlineStr">
+    <row r="17" ht="19.95" customHeight="1" s="127">
+      <c r="A17" s="318" t="inlineStr">
         <is>
           <t>Estado del programa</t>
         </is>
       </c>
-      <c r="B17" s="31" t="n"/>
-      <c r="C17" s="48">
+      <c r="B17" s="97" t="n"/>
+      <c r="C17" s="319">
         <f>IF(E16="","",IF(E16&gt;=G16,"✔ Cumple la meta de cumplimiento","✘ Por debajo de la meta de cumplimiento"))</f>
         <v/>
       </c>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="30" t="n"/>
-      <c r="F17" s="30" t="n"/>
-      <c r="G17" s="31" t="n"/>
-      <c r="H17" s="48">
+      <c r="D17" s="98" t="n"/>
+      <c r="E17" s="98" t="n"/>
+      <c r="F17" s="98" t="n"/>
+      <c r="G17" s="97" t="n"/>
+      <c r="H17" s="319">
         <f>IF(L16="","",IF(L16&gt;=N16,"✔ Cobertura en meta","✘ Cobertura por debajo de la meta"))</f>
         <v/>
       </c>
-      <c r="I17" s="30" t="n"/>
-      <c r="J17" s="30" t="n"/>
-      <c r="K17" s="31" t="n"/>
-      <c r="L17" s="48">
+      <c r="I17" s="98" t="n"/>
+      <c r="J17" s="98" t="n"/>
+      <c r="K17" s="97" t="n"/>
+      <c r="L17" s="319">
         <f>IF(P16="","",IF(P16&gt;=Q16,"✔ Eficacia en meta","✘ Eficacia por debajo de la meta"))</f>
         <v/>
       </c>
-      <c r="M17" s="30" t="n"/>
-      <c r="N17" s="30" t="n"/>
-      <c r="O17" s="30" t="n"/>
-      <c r="P17" s="30" t="n"/>
-      <c r="Q17" s="31" t="n"/>
-    </row>
-    <row r="18" ht="16.5" customHeight="1" s="70">
-      <c r="A18" s="54" t="inlineStr">
+      <c r="M17" s="98" t="n"/>
+      <c r="N17" s="98" t="n"/>
+      <c r="O17" s="98" t="n"/>
+      <c r="P17" s="98" t="n"/>
+      <c r="Q17" s="97" t="n"/>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" s="127">
+      <c r="A18" s="137" t="inlineStr">
         <is>
           <t>3. MATRIZ DE CAPACITACIÓN</t>
         </is>
       </c>
-      <c r="B18" s="38" t="n"/>
-      <c r="C18" s="38" t="n"/>
-      <c r="D18" s="38" t="n"/>
-      <c r="E18" s="38" t="n"/>
-      <c r="F18" s="38" t="n"/>
-      <c r="G18" s="38" t="n"/>
-      <c r="H18" s="38" t="n"/>
-      <c r="I18" s="38" t="n"/>
-      <c r="J18" s="38" t="n"/>
-      <c r="K18" s="38" t="n"/>
-      <c r="L18" s="38" t="n"/>
-      <c r="M18" s="38" t="n"/>
-      <c r="N18" s="38" t="n"/>
-      <c r="O18" s="38" t="n"/>
-      <c r="P18" s="38" t="n"/>
-      <c r="Q18" s="47" t="n"/>
-    </row>
-    <row r="19" ht="30" customHeight="1" s="70">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="B18" s="98" t="n"/>
+      <c r="C18" s="98" t="n"/>
+      <c r="D18" s="98" t="n"/>
+      <c r="E18" s="98" t="n"/>
+      <c r="F18" s="98" t="n"/>
+      <c r="G18" s="98" t="n"/>
+      <c r="H18" s="98" t="n"/>
+      <c r="I18" s="98" t="n"/>
+      <c r="J18" s="98" t="n"/>
+      <c r="K18" s="98" t="n"/>
+      <c r="L18" s="98" t="n"/>
+      <c r="M18" s="98" t="n"/>
+      <c r="N18" s="98" t="n"/>
+      <c r="O18" s="98" t="n"/>
+      <c r="P18" s="98" t="n"/>
+      <c r="Q18" s="97" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" s="127">
+      <c r="A19" s="74" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B19" s="74" t="inlineStr">
         <is>
           <t>Tema de la capacitación</t>
         </is>
       </c>
-      <c r="C19" s="34" t="inlineStr">
+      <c r="C19" s="74" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="D19" s="34" t="inlineStr">
+      <c r="D19" s="74" t="inlineStr">
         <is>
           <t>Dirigida a</t>
         </is>
       </c>
-      <c r="E19" s="34" t="inlineStr">
+      <c r="E19" s="74" t="inlineStr">
         <is>
           <t>Fecha programada</t>
         </is>
       </c>
-      <c r="F19" s="34" t="inlineStr">
+      <c r="F19" s="74" t="inlineStr">
         <is>
           <t>Fecha ejecutada</t>
         </is>
       </c>
-      <c r="G19" s="34" t="inlineStr">
+      <c r="G19" s="74" t="inlineStr">
         <is>
           <t>Capacitador / entidad</t>
         </is>
       </c>
-      <c r="H19" s="34" t="inlineStr">
+      <c r="H19" s="74" t="inlineStr">
         <is>
           <t>Duración (h)</t>
         </is>
       </c>
-      <c r="I19" s="34" t="inlineStr">
+      <c r="I19" s="74" t="inlineStr">
         <is>
           <t>Personas convocadas</t>
         </is>
       </c>
-      <c r="J19" s="34" t="inlineStr">
+      <c r="J19" s="74" t="inlineStr">
         <is>
           <t>Personas asistentes</t>
         </is>
       </c>
-      <c r="K19" s="34" t="inlineStr">
+      <c r="K19" s="74" t="inlineStr">
         <is>
           <t>Cobertura %</t>
         </is>
       </c>
-      <c r="L19" s="34" t="inlineStr">
+      <c r="L19" s="74" t="inlineStr">
         <is>
           <t>Personas evaluadas</t>
         </is>
       </c>
-      <c r="M19" s="34" t="inlineStr">
+      <c r="M19" s="74" t="inlineStr">
         <is>
           <t>Personas aprobadas</t>
         </is>
       </c>
-      <c r="N19" s="34" t="inlineStr">
+      <c r="N19" s="74" t="inlineStr">
         <is>
           <t>Eficacia %</t>
         </is>
       </c>
-      <c r="O19" s="34" t="inlineStr">
+      <c r="O19" s="74" t="inlineStr">
         <is>
           <t>Lista de asistencia N°</t>
         </is>
       </c>
-      <c r="P19" s="34" t="inlineStr">
+      <c r="P19" s="74" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="Q19" s="34" t="inlineStr">
+      <c r="Q19" s="74" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1" s="70">
-      <c r="A20" s="57" t="n">
+    <row r="20" ht="18" customHeight="1" s="127">
+      <c r="A20" s="126" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="29" t="n"/>
-      <c r="C20" s="29" t="n"/>
-      <c r="D20" s="29" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="29" t="n"/>
-      <c r="H20" s="57" t="n"/>
-      <c r="I20" s="57" t="n"/>
-      <c r="J20" s="57" t="n"/>
-      <c r="K20" s="28">
+      <c r="B20" s="76" t="n"/>
+      <c r="C20" s="76" t="n"/>
+      <c r="D20" s="76" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="76" t="n"/>
+      <c r="H20" s="126" t="n"/>
+      <c r="I20" s="126" t="n"/>
+      <c r="J20" s="126" t="n"/>
+      <c r="K20" s="24">
         <f>IFERROR(J20/I20,"")</f>
         <v/>
       </c>
-      <c r="L20" s="57" t="n"/>
-      <c r="M20" s="57" t="n"/>
-      <c r="N20" s="28">
+      <c r="L20" s="126" t="n"/>
+      <c r="M20" s="126" t="n"/>
+      <c r="N20" s="24">
         <f>IFERROR(M20/L20,"")</f>
         <v/>
       </c>
-      <c r="O20" s="57" t="n"/>
-      <c r="P20" s="57" t="n"/>
-      <c r="Q20" s="29" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1" s="70">
-      <c r="A21" s="57" t="n">
+      <c r="O20" s="126" t="n"/>
+      <c r="P20" s="126" t="n"/>
+      <c r="Q20" s="76" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="127">
+      <c r="A21" s="126" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="29" t="n"/>
-      <c r="C21" s="29" t="n"/>
-      <c r="D21" s="29" t="n"/>
-      <c r="E21" s="27" t="n"/>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="29" t="n"/>
-      <c r="H21" s="57" t="n"/>
-      <c r="I21" s="57" t="n"/>
-      <c r="J21" s="57" t="n"/>
-      <c r="K21" s="28">
+      <c r="B21" s="76" t="n"/>
+      <c r="C21" s="76" t="n"/>
+      <c r="D21" s="76" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="76" t="n"/>
+      <c r="H21" s="126" t="n"/>
+      <c r="I21" s="126" t="n"/>
+      <c r="J21" s="126" t="n"/>
+      <c r="K21" s="24">
         <f>IFERROR(J21/I21,"")</f>
         <v/>
       </c>
-      <c r="L21" s="57" t="n"/>
-      <c r="M21" s="57" t="n"/>
-      <c r="N21" s="28">
+      <c r="L21" s="126" t="n"/>
+      <c r="M21" s="126" t="n"/>
+      <c r="N21" s="24">
         <f>IFERROR(M21/L21,"")</f>
         <v/>
       </c>
-      <c r="O21" s="57" t="n"/>
-      <c r="P21" s="57" t="n"/>
-      <c r="Q21" s="29" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" s="70">
-      <c r="A22" s="57" t="n">
+      <c r="O21" s="126" t="n"/>
+      <c r="P21" s="126" t="n"/>
+      <c r="Q21" s="76" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="127">
+      <c r="A22" s="126" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="29" t="n"/>
-      <c r="C22" s="29" t="n"/>
-      <c r="D22" s="29" t="n"/>
-      <c r="E22" s="27" t="n"/>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="29" t="n"/>
-      <c r="H22" s="57" t="n"/>
-      <c r="I22" s="57" t="n"/>
-      <c r="J22" s="57" t="n"/>
-      <c r="K22" s="28">
+      <c r="B22" s="76" t="n"/>
+      <c r="C22" s="76" t="n"/>
+      <c r="D22" s="76" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="76" t="n"/>
+      <c r="H22" s="126" t="n"/>
+      <c r="I22" s="126" t="n"/>
+      <c r="J22" s="126" t="n"/>
+      <c r="K22" s="24">
         <f>IFERROR(J22/I22,"")</f>
         <v/>
       </c>
-      <c r="L22" s="57" t="n"/>
-      <c r="M22" s="57" t="n"/>
-      <c r="N22" s="28">
+      <c r="L22" s="126" t="n"/>
+      <c r="M22" s="126" t="n"/>
+      <c r="N22" s="24">
         <f>IFERROR(M22/L22,"")</f>
         <v/>
       </c>
-      <c r="O22" s="57" t="n"/>
-      <c r="P22" s="57" t="n"/>
-      <c r="Q22" s="29" t="n"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" s="70">
-      <c r="A23" s="57" t="n">
+      <c r="O22" s="126" t="n"/>
+      <c r="P22" s="126" t="n"/>
+      <c r="Q22" s="76" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="127">
+      <c r="A23" s="126" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="29" t="n"/>
-      <c r="C23" s="29" t="n"/>
-      <c r="D23" s="29" t="n"/>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="29" t="n"/>
-      <c r="H23" s="57" t="n"/>
-      <c r="I23" s="57" t="n"/>
-      <c r="J23" s="57" t="n"/>
-      <c r="K23" s="28">
+      <c r="B23" s="76" t="n"/>
+      <c r="C23" s="76" t="n"/>
+      <c r="D23" s="76" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="76" t="n"/>
+      <c r="H23" s="126" t="n"/>
+      <c r="I23" s="126" t="n"/>
+      <c r="J23" s="126" t="n"/>
+      <c r="K23" s="24">
         <f>IFERROR(J23/I23,"")</f>
         <v/>
       </c>
-      <c r="L23" s="57" t="n"/>
-      <c r="M23" s="57" t="n"/>
-      <c r="N23" s="28">
+      <c r="L23" s="126" t="n"/>
+      <c r="M23" s="126" t="n"/>
+      <c r="N23" s="24">
         <f>IFERROR(M23/L23,"")</f>
         <v/>
       </c>
-      <c r="O23" s="57" t="n"/>
-      <c r="P23" s="57" t="n"/>
-      <c r="Q23" s="29" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1" s="70">
-      <c r="A24" s="57" t="n">
+      <c r="O23" s="126" t="n"/>
+      <c r="P23" s="126" t="n"/>
+      <c r="Q23" s="76" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="127">
+      <c r="A24" s="126" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="29" t="n"/>
-      <c r="C24" s="29" t="n"/>
-      <c r="D24" s="29" t="n"/>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="29" t="n"/>
-      <c r="H24" s="57" t="n"/>
-      <c r="I24" s="57" t="n"/>
-      <c r="J24" s="57" t="n"/>
-      <c r="K24" s="28">
+      <c r="B24" s="76" t="n"/>
+      <c r="C24" s="76" t="n"/>
+      <c r="D24" s="76" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="76" t="n"/>
+      <c r="H24" s="126" t="n"/>
+      <c r="I24" s="126" t="n"/>
+      <c r="J24" s="126" t="n"/>
+      <c r="K24" s="24">
         <f>IFERROR(J24/I24,"")</f>
         <v/>
       </c>
-      <c r="L24" s="57" t="n"/>
-      <c r="M24" s="57" t="n"/>
-      <c r="N24" s="28">
+      <c r="L24" s="126" t="n"/>
+      <c r="M24" s="126" t="n"/>
+      <c r="N24" s="24">
         <f>IFERROR(M24/L24,"")</f>
         <v/>
       </c>
-      <c r="O24" s="57" t="n"/>
-      <c r="P24" s="57" t="n"/>
-      <c r="Q24" s="29" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" s="70">
-      <c r="A25" s="57" t="n">
+      <c r="O24" s="126" t="n"/>
+      <c r="P24" s="126" t="n"/>
+      <c r="Q24" s="76" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="127">
+      <c r="A25" s="126" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="29" t="n"/>
-      <c r="C25" s="29" t="n"/>
-      <c r="D25" s="29" t="n"/>
-      <c r="E25" s="27" t="n"/>
-      <c r="F25" s="27" t="n"/>
-      <c r="G25" s="29" t="n"/>
-      <c r="H25" s="57" t="n"/>
-      <c r="I25" s="57" t="n"/>
-      <c r="J25" s="57" t="n"/>
-      <c r="K25" s="28">
+      <c r="B25" s="76" t="n"/>
+      <c r="C25" s="76" t="n"/>
+      <c r="D25" s="76" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="76" t="n"/>
+      <c r="H25" s="126" t="n"/>
+      <c r="I25" s="126" t="n"/>
+      <c r="J25" s="126" t="n"/>
+      <c r="K25" s="24">
         <f>IFERROR(J25/I25,"")</f>
         <v/>
       </c>
-      <c r="L25" s="57" t="n"/>
-      <c r="M25" s="57" t="n"/>
-      <c r="N25" s="28">
+      <c r="L25" s="126" t="n"/>
+      <c r="M25" s="126" t="n"/>
+      <c r="N25" s="24">
         <f>IFERROR(M25/L25,"")</f>
         <v/>
       </c>
-      <c r="O25" s="57" t="n"/>
-      <c r="P25" s="57" t="n"/>
-      <c r="Q25" s="29" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" s="70">
-      <c r="A26" s="57" t="n">
+      <c r="O25" s="126" t="n"/>
+      <c r="P25" s="126" t="n"/>
+      <c r="Q25" s="76" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="127">
+      <c r="A26" s="126" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="29" t="n"/>
-      <c r="C26" s="29" t="n"/>
-      <c r="D26" s="29" t="n"/>
-      <c r="E26" s="27" t="n"/>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="29" t="n"/>
-      <c r="H26" s="57" t="n"/>
-      <c r="I26" s="57" t="n"/>
-      <c r="J26" s="57" t="n"/>
-      <c r="K26" s="28">
+      <c r="B26" s="76" t="n"/>
+      <c r="C26" s="76" t="n"/>
+      <c r="D26" s="76" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="76" t="n"/>
+      <c r="H26" s="126" t="n"/>
+      <c r="I26" s="126" t="n"/>
+      <c r="J26" s="126" t="n"/>
+      <c r="K26" s="24">
         <f>IFERROR(J26/I26,"")</f>
         <v/>
       </c>
-      <c r="L26" s="57" t="n"/>
-      <c r="M26" s="57" t="n"/>
-      <c r="N26" s="28">
+      <c r="L26" s="126" t="n"/>
+      <c r="M26" s="126" t="n"/>
+      <c r="N26" s="24">
         <f>IFERROR(M26/L26,"")</f>
         <v/>
       </c>
-      <c r="O26" s="57" t="n"/>
-      <c r="P26" s="57" t="n"/>
-      <c r="Q26" s="29" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" s="70">
-      <c r="A27" s="57" t="n">
+      <c r="O26" s="126" t="n"/>
+      <c r="P26" s="126" t="n"/>
+      <c r="Q26" s="76" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="127">
+      <c r="A27" s="126" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="29" t="n"/>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="29" t="n"/>
-      <c r="E27" s="27" t="n"/>
-      <c r="F27" s="27" t="n"/>
-      <c r="G27" s="29" t="n"/>
-      <c r="H27" s="57" t="n"/>
-      <c r="I27" s="57" t="n"/>
-      <c r="J27" s="57" t="n"/>
-      <c r="K27" s="28">
+      <c r="B27" s="76" t="n"/>
+      <c r="C27" s="76" t="n"/>
+      <c r="D27" s="76" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="76" t="n"/>
+      <c r="H27" s="126" t="n"/>
+      <c r="I27" s="126" t="n"/>
+      <c r="J27" s="126" t="n"/>
+      <c r="K27" s="24">
         <f>IFERROR(J27/I27,"")</f>
         <v/>
       </c>
-      <c r="L27" s="57" t="n"/>
-      <c r="M27" s="57" t="n"/>
-      <c r="N27" s="28">
+      <c r="L27" s="126" t="n"/>
+      <c r="M27" s="126" t="n"/>
+      <c r="N27" s="24">
         <f>IFERROR(M27/L27,"")</f>
         <v/>
       </c>
-      <c r="O27" s="57" t="n"/>
-      <c r="P27" s="57" t="n"/>
-      <c r="Q27" s="29" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" s="70">
-      <c r="A28" s="57" t="n">
+      <c r="O27" s="126" t="n"/>
+      <c r="P27" s="126" t="n"/>
+      <c r="Q27" s="76" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="127">
+      <c r="A28" s="126" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="29" t="n"/>
-      <c r="C28" s="29" t="n"/>
-      <c r="D28" s="29" t="n"/>
-      <c r="E28" s="27" t="n"/>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="29" t="n"/>
-      <c r="H28" s="57" t="n"/>
-      <c r="I28" s="57" t="n"/>
-      <c r="J28" s="57" t="n"/>
-      <c r="K28" s="28">
+      <c r="B28" s="76" t="n"/>
+      <c r="C28" s="76" t="n"/>
+      <c r="D28" s="76" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="23" t="n"/>
+      <c r="G28" s="76" t="n"/>
+      <c r="H28" s="126" t="n"/>
+      <c r="I28" s="126" t="n"/>
+      <c r="J28" s="126" t="n"/>
+      <c r="K28" s="24">
         <f>IFERROR(J28/I28,"")</f>
         <v/>
       </c>
-      <c r="L28" s="57" t="n"/>
-      <c r="M28" s="57" t="n"/>
-      <c r="N28" s="28">
+      <c r="L28" s="126" t="n"/>
+      <c r="M28" s="126" t="n"/>
+      <c r="N28" s="24">
         <f>IFERROR(M28/L28,"")</f>
         <v/>
       </c>
-      <c r="O28" s="57" t="n"/>
-      <c r="P28" s="57" t="n"/>
-      <c r="Q28" s="29" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1" s="70">
-      <c r="A29" s="57" t="n">
+      <c r="O28" s="126" t="n"/>
+      <c r="P28" s="126" t="n"/>
+      <c r="Q28" s="76" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="127">
+      <c r="A29" s="126" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="29" t="n"/>
-      <c r="C29" s="29" t="n"/>
-      <c r="D29" s="29" t="n"/>
-      <c r="E29" s="27" t="n"/>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="29" t="n"/>
-      <c r="H29" s="57" t="n"/>
-      <c r="I29" s="57" t="n"/>
-      <c r="J29" s="57" t="n"/>
-      <c r="K29" s="28">
+      <c r="B29" s="76" t="n"/>
+      <c r="C29" s="76" t="n"/>
+      <c r="D29" s="76" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="76" t="n"/>
+      <c r="H29" s="126" t="n"/>
+      <c r="I29" s="126" t="n"/>
+      <c r="J29" s="126" t="n"/>
+      <c r="K29" s="24">
         <f>IFERROR(J29/I29,"")</f>
         <v/>
       </c>
-      <c r="L29" s="57" t="n"/>
-      <c r="M29" s="57" t="n"/>
-      <c r="N29" s="28">
+      <c r="L29" s="126" t="n"/>
+      <c r="M29" s="126" t="n"/>
+      <c r="N29" s="24">
         <f>IFERROR(M29/L29,"")</f>
         <v/>
       </c>
-      <c r="O29" s="57" t="n"/>
-      <c r="P29" s="57" t="n"/>
-      <c r="Q29" s="29" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1" s="70">
-      <c r="A30" s="57" t="n">
+      <c r="O29" s="126" t="n"/>
+      <c r="P29" s="126" t="n"/>
+      <c r="Q29" s="76" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1" s="127">
+      <c r="A30" s="126" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="29" t="n"/>
-      <c r="C30" s="29" t="n"/>
-      <c r="D30" s="29" t="n"/>
-      <c r="E30" s="27" t="n"/>
-      <c r="F30" s="27" t="n"/>
-      <c r="G30" s="29" t="n"/>
-      <c r="H30" s="57" t="n"/>
-      <c r="I30" s="57" t="n"/>
-      <c r="J30" s="57" t="n"/>
-      <c r="K30" s="28">
+      <c r="B30" s="76" t="n"/>
+      <c r="C30" s="76" t="n"/>
+      <c r="D30" s="76" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="76" t="n"/>
+      <c r="H30" s="126" t="n"/>
+      <c r="I30" s="126" t="n"/>
+      <c r="J30" s="126" t="n"/>
+      <c r="K30" s="24">
         <f>IFERROR(J30/I30,"")</f>
         <v/>
       </c>
-      <c r="L30" s="57" t="n"/>
-      <c r="M30" s="57" t="n"/>
-      <c r="N30" s="28">
+      <c r="L30" s="126" t="n"/>
+      <c r="M30" s="126" t="n"/>
+      <c r="N30" s="24">
         <f>IFERROR(M30/L30,"")</f>
         <v/>
       </c>
-      <c r="O30" s="57" t="n"/>
-      <c r="P30" s="57" t="n"/>
-      <c r="Q30" s="29" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1" s="70">
-      <c r="A31" s="57" t="n">
+      <c r="O30" s="126" t="n"/>
+      <c r="P30" s="126" t="n"/>
+      <c r="Q30" s="76" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="127">
+      <c r="A31" s="126" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="29" t="n"/>
-      <c r="C31" s="29" t="n"/>
-      <c r="D31" s="29" t="n"/>
-      <c r="E31" s="27" t="n"/>
-      <c r="F31" s="27" t="n"/>
-      <c r="G31" s="29" t="n"/>
-      <c r="H31" s="57" t="n"/>
-      <c r="I31" s="57" t="n"/>
-      <c r="J31" s="57" t="n"/>
-      <c r="K31" s="28">
+      <c r="B31" s="76" t="n"/>
+      <c r="C31" s="76" t="n"/>
+      <c r="D31" s="76" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="76" t="n"/>
+      <c r="H31" s="126" t="n"/>
+      <c r="I31" s="126" t="n"/>
+      <c r="J31" s="126" t="n"/>
+      <c r="K31" s="24">
         <f>IFERROR(J31/I31,"")</f>
         <v/>
       </c>
-      <c r="L31" s="57" t="n"/>
-      <c r="M31" s="57" t="n"/>
-      <c r="N31" s="28">
+      <c r="L31" s="126" t="n"/>
+      <c r="M31" s="126" t="n"/>
+      <c r="N31" s="24">
         <f>IFERROR(M31/L31,"")</f>
         <v/>
       </c>
-      <c r="O31" s="57" t="n"/>
-      <c r="P31" s="57" t="n"/>
-      <c r="Q31" s="29" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1" s="70">
-      <c r="A32" s="57" t="n">
+      <c r="O31" s="126" t="n"/>
+      <c r="P31" s="126" t="n"/>
+      <c r="Q31" s="76" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1" s="127">
+      <c r="A32" s="126" t="n">
         <v>13</v>
       </c>
-      <c r="B32" s="29" t="n"/>
-      <c r="C32" s="29" t="n"/>
-      <c r="D32" s="29" t="n"/>
-      <c r="E32" s="27" t="n"/>
-      <c r="F32" s="27" t="n"/>
-      <c r="G32" s="29" t="n"/>
-      <c r="H32" s="57" t="n"/>
-      <c r="I32" s="57" t="n"/>
-      <c r="J32" s="57" t="n"/>
-      <c r="K32" s="28">
+      <c r="B32" s="76" t="n"/>
+      <c r="C32" s="76" t="n"/>
+      <c r="D32" s="76" t="n"/>
+      <c r="E32" s="23" t="n"/>
+      <c r="F32" s="23" t="n"/>
+      <c r="G32" s="76" t="n"/>
+      <c r="H32" s="126" t="n"/>
+      <c r="I32" s="126" t="n"/>
+      <c r="J32" s="126" t="n"/>
+      <c r="K32" s="24">
         <f>IFERROR(J32/I32,"")</f>
         <v/>
       </c>
-      <c r="L32" s="57" t="n"/>
-      <c r="M32" s="57" t="n"/>
-      <c r="N32" s="28">
+      <c r="L32" s="126" t="n"/>
+      <c r="M32" s="126" t="n"/>
+      <c r="N32" s="24">
         <f>IFERROR(M32/L32,"")</f>
         <v/>
       </c>
-      <c r="O32" s="57" t="n"/>
-      <c r="P32" s="57" t="n"/>
-      <c r="Q32" s="29" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1" s="70">
-      <c r="A33" s="57" t="n">
+      <c r="O32" s="126" t="n"/>
+      <c r="P32" s="126" t="n"/>
+      <c r="Q32" s="76" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="127">
+      <c r="A33" s="126" t="n">
         <v>14</v>
       </c>
-      <c r="B33" s="29" t="n"/>
-      <c r="C33" s="29" t="n"/>
-      <c r="D33" s="29" t="n"/>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="29" t="n"/>
-      <c r="H33" s="57" t="n"/>
-      <c r="I33" s="57" t="n"/>
-      <c r="J33" s="57" t="n"/>
-      <c r="K33" s="28">
+      <c r="B33" s="76" t="n"/>
+      <c r="C33" s="76" t="n"/>
+      <c r="D33" s="76" t="n"/>
+      <c r="E33" s="23" t="n"/>
+      <c r="F33" s="23" t="n"/>
+      <c r="G33" s="76" t="n"/>
+      <c r="H33" s="126" t="n"/>
+      <c r="I33" s="126" t="n"/>
+      <c r="J33" s="126" t="n"/>
+      <c r="K33" s="24">
         <f>IFERROR(J33/I33,"")</f>
         <v/>
       </c>
-      <c r="L33" s="57" t="n"/>
-      <c r="M33" s="57" t="n"/>
-      <c r="N33" s="28">
+      <c r="L33" s="126" t="n"/>
+      <c r="M33" s="126" t="n"/>
+      <c r="N33" s="24">
         <f>IFERROR(M33/L33,"")</f>
         <v/>
       </c>
-      <c r="O33" s="57" t="n"/>
-      <c r="P33" s="57" t="n"/>
-      <c r="Q33" s="29" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1" s="70">
-      <c r="A34" s="57" t="n">
+      <c r="O33" s="126" t="n"/>
+      <c r="P33" s="126" t="n"/>
+      <c r="Q33" s="76" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="127">
+      <c r="A34" s="126" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="29" t="n"/>
-      <c r="C34" s="29" t="n"/>
-      <c r="D34" s="29" t="n"/>
-      <c r="E34" s="27" t="n"/>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="29" t="n"/>
-      <c r="H34" s="57" t="n"/>
-      <c r="I34" s="57" t="n"/>
-      <c r="J34" s="57" t="n"/>
-      <c r="K34" s="28">
+      <c r="B34" s="76" t="n"/>
+      <c r="C34" s="76" t="n"/>
+      <c r="D34" s="76" t="n"/>
+      <c r="E34" s="23" t="n"/>
+      <c r="F34" s="23" t="n"/>
+      <c r="G34" s="76" t="n"/>
+      <c r="H34" s="126" t="n"/>
+      <c r="I34" s="126" t="n"/>
+      <c r="J34" s="126" t="n"/>
+      <c r="K34" s="24">
         <f>IFERROR(J34/I34,"")</f>
         <v/>
       </c>
-      <c r="L34" s="57" t="n"/>
-      <c r="M34" s="57" t="n"/>
-      <c r="N34" s="28">
+      <c r="L34" s="126" t="n"/>
+      <c r="M34" s="126" t="n"/>
+      <c r="N34" s="24">
         <f>IFERROR(M34/L34,"")</f>
         <v/>
       </c>
-      <c r="O34" s="57" t="n"/>
-      <c r="P34" s="57" t="n"/>
-      <c r="Q34" s="29" t="n"/>
-    </row>
-    <row r="35" ht="21" customHeight="1" s="70">
-      <c r="A35" s="60" t="inlineStr">
+      <c r="O34" s="126" t="n"/>
+      <c r="P34" s="126" t="n"/>
+      <c r="Q34" s="76" t="n"/>
+    </row>
+    <row r="35" ht="21" customHeight="1" s="127">
+      <c r="A35" s="128" t="inlineStr">
         <is>
           <t>TOTALES</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n"/>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="30" t="n"/>
-      <c r="F35" s="30" t="n"/>
-      <c r="G35" s="30" t="n"/>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="58">
+      <c r="B35" s="93" t="n"/>
+      <c r="C35" s="93" t="n"/>
+      <c r="D35" s="93" t="n"/>
+      <c r="E35" s="93" t="n"/>
+      <c r="F35" s="93" t="n"/>
+      <c r="G35" s="93" t="n"/>
+      <c r="H35" s="89" t="n"/>
+      <c r="I35" s="178">
         <f>SUM(I20:I34)</f>
         <v/>
       </c>
-      <c r="J35" s="58">
+      <c r="J35" s="178">
         <f>SUM(J20:J34)</f>
         <v/>
       </c>
-      <c r="K35" s="32">
+      <c r="K35" s="180">
         <f>IFERROR(J35/I35,"")</f>
         <v/>
       </c>
-      <c r="L35" s="58">
+      <c r="L35" s="178">
         <f>SUM(L20:L34)</f>
         <v/>
       </c>
-      <c r="M35" s="58">
+      <c r="M35" s="178">
         <f>SUM(M20:M34)</f>
         <v/>
       </c>
-      <c r="N35" s="32">
+      <c r="N35" s="180">
         <f>IFERROR(M35/L35,"")</f>
         <v/>
       </c>
-      <c r="O35" s="42" t="n"/>
-      <c r="P35" s="30" t="n"/>
-      <c r="Q35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="16.5" customHeight="1" s="70">
-      <c r="A36" s="54" t="inlineStr">
+      <c r="O35" s="77" t="n"/>
+      <c r="P35" s="93" t="n"/>
+      <c r="Q35" s="89" t="n"/>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" s="127">
+      <c r="A36" s="137" t="inlineStr">
         <is>
           <t>4. OBSERVACIONES Y SEGUIMIENTO</t>
         </is>
       </c>
-      <c r="B36" s="38" t="n"/>
-      <c r="C36" s="38" t="n"/>
-      <c r="D36" s="38" t="n"/>
-      <c r="E36" s="38" t="n"/>
-      <c r="F36" s="38" t="n"/>
-      <c r="G36" s="38" t="n"/>
-      <c r="H36" s="38" t="n"/>
-      <c r="I36" s="38" t="n"/>
-      <c r="J36" s="38" t="n"/>
-      <c r="K36" s="38" t="n"/>
-      <c r="L36" s="38" t="n"/>
-      <c r="M36" s="38" t="n"/>
-      <c r="N36" s="38" t="n"/>
-      <c r="O36" s="38" t="n"/>
-      <c r="P36" s="38" t="n"/>
-      <c r="Q36" s="47" t="n"/>
-    </row>
-    <row r="37" ht="19.95" customHeight="1" s="70">
-      <c r="A37" s="52" t="n"/>
-      <c r="B37" s="56" t="n"/>
-      <c r="C37" s="56" t="n"/>
-      <c r="D37" s="56" t="n"/>
-      <c r="E37" s="56" t="n"/>
-      <c r="F37" s="56" t="n"/>
-      <c r="G37" s="56" t="n"/>
-      <c r="H37" s="56" t="n"/>
-      <c r="I37" s="56" t="n"/>
-      <c r="J37" s="56" t="n"/>
-      <c r="K37" s="56" t="n"/>
-      <c r="L37" s="56" t="n"/>
-      <c r="M37" s="56" t="n"/>
-      <c r="N37" s="56" t="n"/>
-      <c r="O37" s="56" t="n"/>
-      <c r="P37" s="56" t="n"/>
-      <c r="Q37" s="45" t="n"/>
-    </row>
-    <row r="38" ht="19.95" customHeight="1" s="70">
-      <c r="A38" s="37" t="n"/>
-      <c r="B38" s="38" t="n"/>
-      <c r="C38" s="38" t="n"/>
-      <c r="D38" s="38" t="n"/>
-      <c r="E38" s="38" t="n"/>
-      <c r="F38" s="38" t="n"/>
-      <c r="G38" s="38" t="n"/>
-      <c r="H38" s="38" t="n"/>
-      <c r="I38" s="38" t="n"/>
-      <c r="J38" s="38" t="n"/>
-      <c r="K38" s="38" t="n"/>
-      <c r="L38" s="38" t="n"/>
-      <c r="M38" s="38" t="n"/>
-      <c r="N38" s="38" t="n"/>
-      <c r="O38" s="38" t="n"/>
-      <c r="P38" s="38" t="n"/>
-      <c r="Q38" s="47" t="n"/>
-    </row>
-    <row r="39" ht="16.5" customHeight="1" s="70">
-      <c r="A39" s="54" t="inlineStr">
+      <c r="B36" s="98" t="n"/>
+      <c r="C36" s="98" t="n"/>
+      <c r="D36" s="98" t="n"/>
+      <c r="E36" s="98" t="n"/>
+      <c r="F36" s="98" t="n"/>
+      <c r="G36" s="98" t="n"/>
+      <c r="H36" s="98" t="n"/>
+      <c r="I36" s="98" t="n"/>
+      <c r="J36" s="98" t="n"/>
+      <c r="K36" s="98" t="n"/>
+      <c r="L36" s="98" t="n"/>
+      <c r="M36" s="98" t="n"/>
+      <c r="N36" s="98" t="n"/>
+      <c r="O36" s="98" t="n"/>
+      <c r="P36" s="98" t="n"/>
+      <c r="Q36" s="97" t="n"/>
+    </row>
+    <row r="37" ht="19.95" customHeight="1" s="127">
+      <c r="A37" s="100" t="n"/>
+      <c r="B37" s="104" t="n"/>
+      <c r="C37" s="104" t="n"/>
+      <c r="D37" s="104" t="n"/>
+      <c r="E37" s="104" t="n"/>
+      <c r="F37" s="104" t="n"/>
+      <c r="G37" s="104" t="n"/>
+      <c r="H37" s="104" t="n"/>
+      <c r="I37" s="104" t="n"/>
+      <c r="J37" s="104" t="n"/>
+      <c r="K37" s="104" t="n"/>
+      <c r="L37" s="104" t="n"/>
+      <c r="M37" s="104" t="n"/>
+      <c r="N37" s="104" t="n"/>
+      <c r="O37" s="104" t="n"/>
+      <c r="P37" s="104" t="n"/>
+      <c r="Q37" s="94" t="n"/>
+    </row>
+    <row r="38" ht="19.95" customHeight="1" s="127">
+      <c r="A38" s="96" t="n"/>
+      <c r="B38" s="98" t="n"/>
+      <c r="C38" s="98" t="n"/>
+      <c r="D38" s="98" t="n"/>
+      <c r="E38" s="98" t="n"/>
+      <c r="F38" s="98" t="n"/>
+      <c r="G38" s="98" t="n"/>
+      <c r="H38" s="98" t="n"/>
+      <c r="I38" s="98" t="n"/>
+      <c r="J38" s="98" t="n"/>
+      <c r="K38" s="98" t="n"/>
+      <c r="L38" s="98" t="n"/>
+      <c r="M38" s="98" t="n"/>
+      <c r="N38" s="98" t="n"/>
+      <c r="O38" s="98" t="n"/>
+      <c r="P38" s="98" t="n"/>
+      <c r="Q38" s="97" t="n"/>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" s="127">
+      <c r="A39" s="227" t="inlineStr">
         <is>
           <t>5. FIRMAS</t>
         </is>
       </c>
-      <c r="B39" s="38" t="n"/>
-      <c r="C39" s="38" t="n"/>
-      <c r="D39" s="38" t="n"/>
-      <c r="E39" s="38" t="n"/>
-      <c r="F39" s="38" t="n"/>
-      <c r="G39" s="38" t="n"/>
-      <c r="H39" s="38" t="n"/>
-      <c r="I39" s="38" t="n"/>
-      <c r="J39" s="38" t="n"/>
-      <c r="K39" s="38" t="n"/>
-      <c r="L39" s="38" t="n"/>
-      <c r="M39" s="38" t="n"/>
-      <c r="N39" s="38" t="n"/>
-      <c r="O39" s="38" t="n"/>
-      <c r="P39" s="38" t="n"/>
-      <c r="Q39" s="47" t="n"/>
-    </row>
-    <row r="40" ht="18" customHeight="1" s="70">
-      <c r="A40" s="51" t="inlineStr">
+      <c r="Q39" s="92" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" s="127">
+      <c r="A40" s="263" t="inlineStr">
         <is>
           <t>ELABORÓ — RESPONSABLE SST</t>
         </is>
       </c>
-      <c r="B40" s="30" t="n"/>
-      <c r="C40" s="30" t="n"/>
-      <c r="D40" s="30" t="n"/>
-      <c r="E40" s="30" t="n"/>
-      <c r="F40" s="30" t="n"/>
-      <c r="G40" s="31" t="n"/>
-      <c r="H40" s="51" t="inlineStr">
+      <c r="B40" s="347" t="n"/>
+      <c r="C40" s="347" t="n"/>
+      <c r="D40" s="347" t="n"/>
+      <c r="E40" s="347" t="n"/>
+      <c r="F40" s="347" t="n"/>
+      <c r="G40" s="348" t="n"/>
+      <c r="H40" s="263" t="inlineStr">
         <is>
           <t>REVISÓ — RESIDENTE / DIRECTOR DE OBRA</t>
         </is>
       </c>
-      <c r="I40" s="30" t="n"/>
-      <c r="J40" s="30" t="n"/>
-      <c r="K40" s="30" t="n"/>
-      <c r="L40" s="30" t="n"/>
-      <c r="M40" s="30" t="n"/>
-      <c r="N40" s="31" t="n"/>
-      <c r="O40" s="51" t="inlineStr">
+      <c r="I40" s="347" t="n"/>
+      <c r="J40" s="347" t="n"/>
+      <c r="K40" s="347" t="n"/>
+      <c r="L40" s="347" t="n"/>
+      <c r="M40" s="347" t="n"/>
+      <c r="N40" s="348" t="n"/>
+      <c r="O40" s="263" t="inlineStr">
         <is>
           <t>Vo.Bo. GERENCIA</t>
         </is>
       </c>
-      <c r="P40" s="30" t="n"/>
-      <c r="Q40" s="31" t="n"/>
-    </row>
-    <row r="41" ht="42" customHeight="1" s="70">
-      <c r="A41" s="39" t="inlineStr">
+      <c r="P40" s="347" t="n"/>
+      <c r="Q40" s="348" t="n"/>
+    </row>
+    <row r="41" ht="42" customHeight="1" s="127">
+      <c r="A41" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="B41" s="31" t="n"/>
-      <c r="C41" s="43" t="n"/>
-      <c r="D41" s="30" t="n"/>
-      <c r="E41" s="30" t="n"/>
-      <c r="F41" s="30" t="n"/>
-      <c r="G41" s="31" t="n"/>
-      <c r="H41" s="39" t="inlineStr">
+      <c r="B41" s="97" t="n"/>
+      <c r="C41" s="301" t="n"/>
+      <c r="D41" s="98" t="n"/>
+      <c r="E41" s="98" t="n"/>
+      <c r="F41" s="98" t="n"/>
+      <c r="G41" s="97" t="n"/>
+      <c r="H41" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="I41" s="31" t="n"/>
-      <c r="J41" s="43" t="n"/>
-      <c r="K41" s="30" t="n"/>
-      <c r="L41" s="30" t="n"/>
-      <c r="M41" s="30" t="n"/>
-      <c r="N41" s="31" t="n"/>
-      <c r="O41" s="39" t="inlineStr">
+      <c r="I41" s="97" t="n"/>
+      <c r="J41" s="301" t="n"/>
+      <c r="K41" s="98" t="n"/>
+      <c r="L41" s="98" t="n"/>
+      <c r="M41" s="98" t="n"/>
+      <c r="N41" s="97" t="n"/>
+      <c r="O41" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="P41" s="31" t="n"/>
-      <c r="Q41" s="43" t="n"/>
-    </row>
-    <row r="42" ht="21" customHeight="1" s="70">
-      <c r="A42" s="39" t="inlineStr">
+      <c r="P41" s="97" t="n"/>
+      <c r="Q41" s="301" t="n"/>
+    </row>
+    <row r="42" ht="21" customHeight="1" s="127">
+      <c r="A42" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="B42" s="31" t="n"/>
-      <c r="C42" s="43" t="n"/>
-      <c r="D42" s="30" t="n"/>
-      <c r="E42" s="30" t="n"/>
-      <c r="F42" s="30" t="n"/>
-      <c r="G42" s="31" t="n"/>
-      <c r="H42" s="39" t="inlineStr">
+      <c r="B42" s="89" t="n"/>
+      <c r="C42" s="68" t="n"/>
+      <c r="D42" s="93" t="n"/>
+      <c r="E42" s="93" t="n"/>
+      <c r="F42" s="93" t="n"/>
+      <c r="G42" s="89" t="n"/>
+      <c r="H42" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="I42" s="31" t="n"/>
-      <c r="J42" s="43" t="n"/>
-      <c r="K42" s="30" t="n"/>
-      <c r="L42" s="30" t="n"/>
-      <c r="M42" s="30" t="n"/>
-      <c r="N42" s="31" t="n"/>
-      <c r="O42" s="39" t="inlineStr">
+      <c r="I42" s="89" t="n"/>
+      <c r="J42" s="68" t="n"/>
+      <c r="K42" s="93" t="n"/>
+      <c r="L42" s="93" t="n"/>
+      <c r="M42" s="93" t="n"/>
+      <c r="N42" s="89" t="n"/>
+      <c r="O42" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
-      <c r="P42" s="31" t="n"/>
-      <c r="Q42" s="43" t="n"/>
-    </row>
-    <row r="43" ht="21" customHeight="1" s="70">
-      <c r="A43" s="39" t="inlineStr">
+      <c r="P42" s="89" t="n"/>
+      <c r="Q42" s="68" t="n"/>
+    </row>
+    <row r="43" ht="21" customHeight="1" s="127">
+      <c r="A43" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="B43" s="31" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="30" t="n"/>
-      <c r="E43" s="30" t="n"/>
-      <c r="F43" s="30" t="n"/>
-      <c r="G43" s="31" t="n"/>
-      <c r="H43" s="39" t="inlineStr">
+      <c r="B43" s="89" t="n"/>
+      <c r="C43" s="68" t="n"/>
+      <c r="D43" s="93" t="n"/>
+      <c r="E43" s="93" t="n"/>
+      <c r="F43" s="93" t="n"/>
+      <c r="G43" s="89" t="n"/>
+      <c r="H43" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="I43" s="31" t="n"/>
-      <c r="J43" s="43" t="n"/>
-      <c r="K43" s="30" t="n"/>
-      <c r="L43" s="30" t="n"/>
-      <c r="M43" s="30" t="n"/>
-      <c r="N43" s="31" t="n"/>
-      <c r="O43" s="39" t="inlineStr">
+      <c r="I43" s="89" t="n"/>
+      <c r="J43" s="68" t="n"/>
+      <c r="K43" s="93" t="n"/>
+      <c r="L43" s="93" t="n"/>
+      <c r="M43" s="93" t="n"/>
+      <c r="N43" s="89" t="n"/>
+      <c r="O43" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
-      <c r="P43" s="31" t="n"/>
-      <c r="Q43" s="43" t="n"/>
-    </row>
-    <row r="44" s="64">
-      <c r="A44" s="61" t="inlineStr">
+      <c r="P43" s="89" t="n"/>
+      <c r="Q43" s="68" t="n"/>
+    </row>
+    <row r="44" s="106">
+      <c r="A44" s="25" t="inlineStr">
         <is>
           <t>REV. 04/10/2026</t>
         </is>
       </c>
-      <c r="I44" s="63">
+      <c r="I44" s="105">
         <f>P5</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="E13:G13"/>
     <mergeCell ref="A9:Q9"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E13:G13"/>
-    <mergeCell ref="H13:K13"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A39:Q39"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="H43:I43"/>
     <mergeCell ref="C42:G42"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="O35:Q35"/>
-    <mergeCell ref="O4:Q4"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A37:Q38"/>
     <mergeCell ref="H41:I41"/>
@@ -2496,36 +3671,36 @@
     <mergeCell ref="O41:P41"/>
     <mergeCell ref="I44:Q44"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C43:G43"/>
     <mergeCell ref="A18:Q18"/>
     <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C43:G43"/>
     <mergeCell ref="P7:Q7"/>
     <mergeCell ref="L11:Q11"/>
+    <mergeCell ref="H40:N40"/>
     <mergeCell ref="E15:F15"/>
-    <mergeCell ref="H40:N40"/>
     <mergeCell ref="O43:P43"/>
     <mergeCell ref="H16:I16"/>
     <mergeCell ref="J16:K16"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="O42:P42"/>
+    <mergeCell ref="J41:N41"/>
     <mergeCell ref="D1:Q2"/>
-    <mergeCell ref="J41:N41"/>
     <mergeCell ref="L17:Q17"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="C17:G17"/>
     <mergeCell ref="A14:Q14"/>
     <mergeCell ref="D3:Q3"/>
     <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="N15:O15"/>
     <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="A35:H35"/>
     <mergeCell ref="H17:K17"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="H42:I42"/>
     <mergeCell ref="H11:K11"/>
+    <mergeCell ref="H15:I15"/>
     <mergeCell ref="L13:N13"/>
-    <mergeCell ref="H15:I15"/>
     <mergeCell ref="J43:N43"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="D5:N5"/>

--- a/public/plantilla-capacitaciones.xlsx
+++ b/public/plantilla-capacitaciones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacitaciones" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="39">
+  <numFmts count="0"/>
+  <fonts count="40">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -296,6 +297,10 @@
       <color rgb="FF0B1F33"/>
       <sz val="9"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="20">
@@ -1024,7 +1029,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="379">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
@@ -1928,6 +1933,70 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="3" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="39" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="39" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="14" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2637,11 +2706,11 @@
         </is>
       </c>
       <c r="B11" s="89" t="n"/>
-      <c r="C11" s="161" t="n"/>
-      <c r="D11" s="93" t="n"/>
-      <c r="E11" s="93" t="n"/>
-      <c r="F11" s="93" t="n"/>
-      <c r="G11" s="89" t="n"/>
+      <c r="C11" s="360" t="n"/>
+      <c r="D11" s="361" t="n"/>
+      <c r="E11" s="361" t="n"/>
+      <c r="F11" s="361" t="n"/>
+      <c r="G11" s="362" t="n"/>
       <c r="H11" s="59" t="inlineStr">
         <is>
           <t>Contratista / Empresa</t>
@@ -2650,12 +2719,12 @@
       <c r="I11" s="93" t="n"/>
       <c r="J11" s="93" t="n"/>
       <c r="K11" s="89" t="n"/>
-      <c r="L11" s="68" t="n"/>
-      <c r="M11" s="93" t="n"/>
-      <c r="N11" s="93" t="n"/>
-      <c r="O11" s="93" t="n"/>
-      <c r="P11" s="93" t="n"/>
-      <c r="Q11" s="89" t="n"/>
+      <c r="L11" s="363" t="n"/>
+      <c r="M11" s="361" t="n"/>
+      <c r="N11" s="361" t="n"/>
+      <c r="O11" s="361" t="n"/>
+      <c r="P11" s="361" t="n"/>
+      <c r="Q11" s="362" t="n"/>
     </row>
     <row r="12" ht="19.95" customHeight="1" s="127">
       <c r="A12" s="59" t="inlineStr">
@@ -2664,11 +2733,11 @@
         </is>
       </c>
       <c r="B12" s="89" t="n"/>
-      <c r="C12" s="68" t="n"/>
-      <c r="D12" s="93" t="n"/>
-      <c r="E12" s="93" t="n"/>
-      <c r="F12" s="93" t="n"/>
-      <c r="G12" s="89" t="n"/>
+      <c r="C12" s="363" t="n"/>
+      <c r="D12" s="361" t="n"/>
+      <c r="E12" s="361" t="n"/>
+      <c r="F12" s="361" t="n"/>
+      <c r="G12" s="362" t="n"/>
       <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Responsable del programa SST</t>
@@ -2677,16 +2746,16 @@
       <c r="I12" s="93" t="n"/>
       <c r="J12" s="93" t="n"/>
       <c r="K12" s="89" t="n"/>
-      <c r="L12" s="68" t="n"/>
-      <c r="M12" s="93" t="n"/>
-      <c r="N12" s="89" t="n"/>
+      <c r="L12" s="363" t="n"/>
+      <c r="M12" s="361" t="n"/>
+      <c r="N12" s="362" t="n"/>
       <c r="O12" s="59" t="inlineStr">
         <is>
           <t>Cargo</t>
         </is>
       </c>
-      <c r="P12" s="68" t="n"/>
-      <c r="Q12" s="89" t="n"/>
+      <c r="P12" s="363" t="n"/>
+      <c r="Q12" s="362" t="n"/>
     </row>
     <row r="13" ht="19.95" customHeight="1" s="127">
       <c r="A13" s="59" t="inlineStr">
@@ -2695,15 +2764,15 @@
         </is>
       </c>
       <c r="B13" s="89" t="n"/>
-      <c r="C13" s="69" t="n"/>
+      <c r="C13" s="364" t="n"/>
       <c r="D13" s="59" t="inlineStr">
         <is>
           <t>hasta</t>
         </is>
       </c>
-      <c r="E13" s="69" t="n"/>
-      <c r="F13" s="93" t="n"/>
-      <c r="G13" s="89" t="n"/>
+      <c r="E13" s="364" t="n"/>
+      <c r="F13" s="361" t="n"/>
+      <c r="G13" s="362" t="n"/>
       <c r="H13" s="59" t="inlineStr">
         <is>
           <t>Fecha de actualización</t>
@@ -2712,9 +2781,9 @@
       <c r="I13" s="93" t="n"/>
       <c r="J13" s="93" t="n"/>
       <c r="K13" s="89" t="n"/>
-      <c r="L13" s="69" t="n"/>
-      <c r="M13" s="93" t="n"/>
-      <c r="N13" s="89" t="n"/>
+      <c r="L13" s="364" t="n"/>
+      <c r="M13" s="361" t="n"/>
+      <c r="N13" s="362" t="n"/>
       <c r="Q13" s="94" t="n"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="127">
@@ -2815,7 +2884,7 @@
         <v/>
       </c>
       <c r="F16" s="348" t="n"/>
-      <c r="G16" s="322" t="n">
+      <c r="G16" s="365" t="n">
         <v>0.9</v>
       </c>
       <c r="H16" s="320">
@@ -2833,7 +2902,7 @@
         <v/>
       </c>
       <c r="M16" s="348" t="n"/>
-      <c r="N16" s="323" t="n">
+      <c r="N16" s="366" t="n">
         <v>0.8</v>
       </c>
       <c r="O16" s="89" t="n"/>
@@ -2841,7 +2910,7 @@
         <f>IFERROR(SUM(M20:M34)/SUM(L20:L34),"")</f>
         <v/>
       </c>
-      <c r="Q16" s="323" t="n">
+      <c r="Q16" s="366" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -2852,7 +2921,7 @@
         </is>
       </c>
       <c r="B17" s="97" t="n"/>
-      <c r="C17" s="319">
+      <c r="C17" s="367">
         <f>IF(E16="","",IF(E16&gt;=G16,"✔ Cumple la meta de cumplimiento","✘ Por debajo de la meta de cumplimiento"))</f>
         <v/>
       </c>
@@ -2860,14 +2929,14 @@
       <c r="E17" s="98" t="n"/>
       <c r="F17" s="98" t="n"/>
       <c r="G17" s="97" t="n"/>
-      <c r="H17" s="319">
+      <c r="H17" s="367">
         <f>IF(L16="","",IF(L16&gt;=N16,"✔ Cobertura en meta","✘ Cobertura por debajo de la meta"))</f>
         <v/>
       </c>
       <c r="I17" s="98" t="n"/>
       <c r="J17" s="98" t="n"/>
       <c r="K17" s="97" t="n"/>
-      <c r="L17" s="319">
+      <c r="L17" s="367">
         <f>IF(P16="","",IF(P16&gt;=Q16,"✔ Eficacia en meta","✘ Eficacia por debajo de la meta"))</f>
         <v/>
       </c>
@@ -2988,409 +3057,409 @@
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" s="127">
-      <c r="A20" s="126" t="n">
+      <c r="A20" s="368" t="n">
         <v>1</v>
       </c>
-      <c r="B20" s="76" t="n"/>
-      <c r="C20" s="76" t="n"/>
-      <c r="D20" s="76" t="n"/>
-      <c r="E20" s="23" t="n"/>
-      <c r="F20" s="23" t="n"/>
-      <c r="G20" s="76" t="n"/>
-      <c r="H20" s="126" t="n"/>
-      <c r="I20" s="126" t="n"/>
-      <c r="J20" s="126" t="n"/>
-      <c r="K20" s="24">
+      <c r="B20" s="363" t="n"/>
+      <c r="C20" s="363" t="n"/>
+      <c r="D20" s="363" t="n"/>
+      <c r="E20" s="369" t="n"/>
+      <c r="F20" s="369" t="n"/>
+      <c r="G20" s="363" t="n"/>
+      <c r="H20" s="370" t="n"/>
+      <c r="I20" s="370" t="n"/>
+      <c r="J20" s="370" t="n"/>
+      <c r="K20" s="371">
         <f>IFERROR(J20/I20,"")</f>
         <v/>
       </c>
-      <c r="L20" s="126" t="n"/>
-      <c r="M20" s="126" t="n"/>
-      <c r="N20" s="24">
+      <c r="L20" s="370" t="n"/>
+      <c r="M20" s="370" t="n"/>
+      <c r="N20" s="371">
         <f>IFERROR(M20/L20,"")</f>
         <v/>
       </c>
-      <c r="O20" s="126" t="n"/>
-      <c r="P20" s="126" t="n"/>
-      <c r="Q20" s="76" t="n"/>
+      <c r="O20" s="370" t="n"/>
+      <c r="P20" s="370" t="n"/>
+      <c r="Q20" s="363" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="127">
-      <c r="A21" s="126" t="n">
+      <c r="A21" s="368" t="n">
         <v>2</v>
       </c>
-      <c r="B21" s="76" t="n"/>
-      <c r="C21" s="76" t="n"/>
-      <c r="D21" s="76" t="n"/>
-      <c r="E21" s="23" t="n"/>
-      <c r="F21" s="23" t="n"/>
-      <c r="G21" s="76" t="n"/>
-      <c r="H21" s="126" t="n"/>
-      <c r="I21" s="126" t="n"/>
-      <c r="J21" s="126" t="n"/>
-      <c r="K21" s="24">
+      <c r="B21" s="363" t="n"/>
+      <c r="C21" s="363" t="n"/>
+      <c r="D21" s="363" t="n"/>
+      <c r="E21" s="369" t="n"/>
+      <c r="F21" s="369" t="n"/>
+      <c r="G21" s="363" t="n"/>
+      <c r="H21" s="370" t="n"/>
+      <c r="I21" s="370" t="n"/>
+      <c r="J21" s="370" t="n"/>
+      <c r="K21" s="371">
         <f>IFERROR(J21/I21,"")</f>
         <v/>
       </c>
-      <c r="L21" s="126" t="n"/>
-      <c r="M21" s="126" t="n"/>
-      <c r="N21" s="24">
+      <c r="L21" s="370" t="n"/>
+      <c r="M21" s="370" t="n"/>
+      <c r="N21" s="371">
         <f>IFERROR(M21/L21,"")</f>
         <v/>
       </c>
-      <c r="O21" s="126" t="n"/>
-      <c r="P21" s="126" t="n"/>
-      <c r="Q21" s="76" t="n"/>
+      <c r="O21" s="370" t="n"/>
+      <c r="P21" s="370" t="n"/>
+      <c r="Q21" s="363" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1" s="127">
-      <c r="A22" s="126" t="n">
+      <c r="A22" s="368" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="76" t="n"/>
-      <c r="C22" s="76" t="n"/>
-      <c r="D22" s="76" t="n"/>
-      <c r="E22" s="23" t="n"/>
-      <c r="F22" s="23" t="n"/>
-      <c r="G22" s="76" t="n"/>
-      <c r="H22" s="126" t="n"/>
-      <c r="I22" s="126" t="n"/>
-      <c r="J22" s="126" t="n"/>
-      <c r="K22" s="24">
+      <c r="B22" s="363" t="n"/>
+      <c r="C22" s="363" t="n"/>
+      <c r="D22" s="363" t="n"/>
+      <c r="E22" s="369" t="n"/>
+      <c r="F22" s="369" t="n"/>
+      <c r="G22" s="363" t="n"/>
+      <c r="H22" s="370" t="n"/>
+      <c r="I22" s="370" t="n"/>
+      <c r="J22" s="370" t="n"/>
+      <c r="K22" s="371">
         <f>IFERROR(J22/I22,"")</f>
         <v/>
       </c>
-      <c r="L22" s="126" t="n"/>
-      <c r="M22" s="126" t="n"/>
-      <c r="N22" s="24">
+      <c r="L22" s="370" t="n"/>
+      <c r="M22" s="370" t="n"/>
+      <c r="N22" s="371">
         <f>IFERROR(M22/L22,"")</f>
         <v/>
       </c>
-      <c r="O22" s="126" t="n"/>
-      <c r="P22" s="126" t="n"/>
-      <c r="Q22" s="76" t="n"/>
+      <c r="O22" s="370" t="n"/>
+      <c r="P22" s="370" t="n"/>
+      <c r="Q22" s="363" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="127">
-      <c r="A23" s="126" t="n">
+      <c r="A23" s="368" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="76" t="n"/>
-      <c r="C23" s="76" t="n"/>
-      <c r="D23" s="76" t="n"/>
-      <c r="E23" s="23" t="n"/>
-      <c r="F23" s="23" t="n"/>
-      <c r="G23" s="76" t="n"/>
-      <c r="H23" s="126" t="n"/>
-      <c r="I23" s="126" t="n"/>
-      <c r="J23" s="126" t="n"/>
-      <c r="K23" s="24">
+      <c r="B23" s="363" t="n"/>
+      <c r="C23" s="363" t="n"/>
+      <c r="D23" s="363" t="n"/>
+      <c r="E23" s="369" t="n"/>
+      <c r="F23" s="369" t="n"/>
+      <c r="G23" s="363" t="n"/>
+      <c r="H23" s="370" t="n"/>
+      <c r="I23" s="370" t="n"/>
+      <c r="J23" s="370" t="n"/>
+      <c r="K23" s="371">
         <f>IFERROR(J23/I23,"")</f>
         <v/>
       </c>
-      <c r="L23" s="126" t="n"/>
-      <c r="M23" s="126" t="n"/>
-      <c r="N23" s="24">
+      <c r="L23" s="370" t="n"/>
+      <c r="M23" s="370" t="n"/>
+      <c r="N23" s="371">
         <f>IFERROR(M23/L23,"")</f>
         <v/>
       </c>
-      <c r="O23" s="126" t="n"/>
-      <c r="P23" s="126" t="n"/>
-      <c r="Q23" s="76" t="n"/>
+      <c r="O23" s="370" t="n"/>
+      <c r="P23" s="370" t="n"/>
+      <c r="Q23" s="363" t="n"/>
     </row>
     <row r="24" ht="18" customHeight="1" s="127">
-      <c r="A24" s="126" t="n">
+      <c r="A24" s="368" t="n">
         <v>5</v>
       </c>
-      <c r="B24" s="76" t="n"/>
-      <c r="C24" s="76" t="n"/>
-      <c r="D24" s="76" t="n"/>
-      <c r="E24" s="23" t="n"/>
-      <c r="F24" s="23" t="n"/>
-      <c r="G24" s="76" t="n"/>
-      <c r="H24" s="126" t="n"/>
-      <c r="I24" s="126" t="n"/>
-      <c r="J24" s="126" t="n"/>
-      <c r="K24" s="24">
+      <c r="B24" s="363" t="n"/>
+      <c r="C24" s="363" t="n"/>
+      <c r="D24" s="363" t="n"/>
+      <c r="E24" s="369" t="n"/>
+      <c r="F24" s="369" t="n"/>
+      <c r="G24" s="363" t="n"/>
+      <c r="H24" s="370" t="n"/>
+      <c r="I24" s="370" t="n"/>
+      <c r="J24" s="370" t="n"/>
+      <c r="K24" s="371">
         <f>IFERROR(J24/I24,"")</f>
         <v/>
       </c>
-      <c r="L24" s="126" t="n"/>
-      <c r="M24" s="126" t="n"/>
-      <c r="N24" s="24">
+      <c r="L24" s="370" t="n"/>
+      <c r="M24" s="370" t="n"/>
+      <c r="N24" s="371">
         <f>IFERROR(M24/L24,"")</f>
         <v/>
       </c>
-      <c r="O24" s="126" t="n"/>
-      <c r="P24" s="126" t="n"/>
-      <c r="Q24" s="76" t="n"/>
+      <c r="O24" s="370" t="n"/>
+      <c r="P24" s="370" t="n"/>
+      <c r="Q24" s="363" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1" s="127">
-      <c r="A25" s="126" t="n">
+      <c r="A25" s="368" t="n">
         <v>6</v>
       </c>
-      <c r="B25" s="76" t="n"/>
-      <c r="C25" s="76" t="n"/>
-      <c r="D25" s="76" t="n"/>
-      <c r="E25" s="23" t="n"/>
-      <c r="F25" s="23" t="n"/>
-      <c r="G25" s="76" t="n"/>
-      <c r="H25" s="126" t="n"/>
-      <c r="I25" s="126" t="n"/>
-      <c r="J25" s="126" t="n"/>
-      <c r="K25" s="24">
+      <c r="B25" s="363" t="n"/>
+      <c r="C25" s="363" t="n"/>
+      <c r="D25" s="363" t="n"/>
+      <c r="E25" s="369" t="n"/>
+      <c r="F25" s="369" t="n"/>
+      <c r="G25" s="363" t="n"/>
+      <c r="H25" s="370" t="n"/>
+      <c r="I25" s="370" t="n"/>
+      <c r="J25" s="370" t="n"/>
+      <c r="K25" s="371">
         <f>IFERROR(J25/I25,"")</f>
         <v/>
       </c>
-      <c r="L25" s="126" t="n"/>
-      <c r="M25" s="126" t="n"/>
-      <c r="N25" s="24">
+      <c r="L25" s="370" t="n"/>
+      <c r="M25" s="370" t="n"/>
+      <c r="N25" s="371">
         <f>IFERROR(M25/L25,"")</f>
         <v/>
       </c>
-      <c r="O25" s="126" t="n"/>
-      <c r="P25" s="126" t="n"/>
-      <c r="Q25" s="76" t="n"/>
+      <c r="O25" s="370" t="n"/>
+      <c r="P25" s="370" t="n"/>
+      <c r="Q25" s="363" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1" s="127">
-      <c r="A26" s="126" t="n">
+      <c r="A26" s="368" t="n">
         <v>7</v>
       </c>
-      <c r="B26" s="76" t="n"/>
-      <c r="C26" s="76" t="n"/>
-      <c r="D26" s="76" t="n"/>
-      <c r="E26" s="23" t="n"/>
-      <c r="F26" s="23" t="n"/>
-      <c r="G26" s="76" t="n"/>
-      <c r="H26" s="126" t="n"/>
-      <c r="I26" s="126" t="n"/>
-      <c r="J26" s="126" t="n"/>
-      <c r="K26" s="24">
+      <c r="B26" s="363" t="n"/>
+      <c r="C26" s="363" t="n"/>
+      <c r="D26" s="363" t="n"/>
+      <c r="E26" s="369" t="n"/>
+      <c r="F26" s="369" t="n"/>
+      <c r="G26" s="363" t="n"/>
+      <c r="H26" s="370" t="n"/>
+      <c r="I26" s="370" t="n"/>
+      <c r="J26" s="370" t="n"/>
+      <c r="K26" s="371">
         <f>IFERROR(J26/I26,"")</f>
         <v/>
       </c>
-      <c r="L26" s="126" t="n"/>
-      <c r="M26" s="126" t="n"/>
-      <c r="N26" s="24">
+      <c r="L26" s="370" t="n"/>
+      <c r="M26" s="370" t="n"/>
+      <c r="N26" s="371">
         <f>IFERROR(M26/L26,"")</f>
         <v/>
       </c>
-      <c r="O26" s="126" t="n"/>
-      <c r="P26" s="126" t="n"/>
-      <c r="Q26" s="76" t="n"/>
+      <c r="O26" s="370" t="n"/>
+      <c r="P26" s="370" t="n"/>
+      <c r="Q26" s="363" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="127">
-      <c r="A27" s="126" t="n">
+      <c r="A27" s="368" t="n">
         <v>8</v>
       </c>
-      <c r="B27" s="76" t="n"/>
-      <c r="C27" s="76" t="n"/>
-      <c r="D27" s="76" t="n"/>
-      <c r="E27" s="23" t="n"/>
-      <c r="F27" s="23" t="n"/>
-      <c r="G27" s="76" t="n"/>
-      <c r="H27" s="126" t="n"/>
-      <c r="I27" s="126" t="n"/>
-      <c r="J27" s="126" t="n"/>
-      <c r="K27" s="24">
+      <c r="B27" s="363" t="n"/>
+      <c r="C27" s="363" t="n"/>
+      <c r="D27" s="363" t="n"/>
+      <c r="E27" s="369" t="n"/>
+      <c r="F27" s="369" t="n"/>
+      <c r="G27" s="363" t="n"/>
+      <c r="H27" s="370" t="n"/>
+      <c r="I27" s="370" t="n"/>
+      <c r="J27" s="370" t="n"/>
+      <c r="K27" s="371">
         <f>IFERROR(J27/I27,"")</f>
         <v/>
       </c>
-      <c r="L27" s="126" t="n"/>
-      <c r="M27" s="126" t="n"/>
-      <c r="N27" s="24">
+      <c r="L27" s="370" t="n"/>
+      <c r="M27" s="370" t="n"/>
+      <c r="N27" s="371">
         <f>IFERROR(M27/L27,"")</f>
         <v/>
       </c>
-      <c r="O27" s="126" t="n"/>
-      <c r="P27" s="126" t="n"/>
-      <c r="Q27" s="76" t="n"/>
+      <c r="O27" s="370" t="n"/>
+      <c r="P27" s="370" t="n"/>
+      <c r="Q27" s="363" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="127">
-      <c r="A28" s="126" t="n">
+      <c r="A28" s="368" t="n">
         <v>9</v>
       </c>
-      <c r="B28" s="76" t="n"/>
-      <c r="C28" s="76" t="n"/>
-      <c r="D28" s="76" t="n"/>
-      <c r="E28" s="23" t="n"/>
-      <c r="F28" s="23" t="n"/>
-      <c r="G28" s="76" t="n"/>
-      <c r="H28" s="126" t="n"/>
-      <c r="I28" s="126" t="n"/>
-      <c r="J28" s="126" t="n"/>
-      <c r="K28" s="24">
+      <c r="B28" s="363" t="n"/>
+      <c r="C28" s="363" t="n"/>
+      <c r="D28" s="363" t="n"/>
+      <c r="E28" s="369" t="n"/>
+      <c r="F28" s="369" t="n"/>
+      <c r="G28" s="363" t="n"/>
+      <c r="H28" s="370" t="n"/>
+      <c r="I28" s="370" t="n"/>
+      <c r="J28" s="370" t="n"/>
+      <c r="K28" s="371">
         <f>IFERROR(J28/I28,"")</f>
         <v/>
       </c>
-      <c r="L28" s="126" t="n"/>
-      <c r="M28" s="126" t="n"/>
-      <c r="N28" s="24">
+      <c r="L28" s="370" t="n"/>
+      <c r="M28" s="370" t="n"/>
+      <c r="N28" s="371">
         <f>IFERROR(M28/L28,"")</f>
         <v/>
       </c>
-      <c r="O28" s="126" t="n"/>
-      <c r="P28" s="126" t="n"/>
-      <c r="Q28" s="76" t="n"/>
+      <c r="O28" s="370" t="n"/>
+      <c r="P28" s="370" t="n"/>
+      <c r="Q28" s="363" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="127">
-      <c r="A29" s="126" t="n">
+      <c r="A29" s="368" t="n">
         <v>10</v>
       </c>
-      <c r="B29" s="76" t="n"/>
-      <c r="C29" s="76" t="n"/>
-      <c r="D29" s="76" t="n"/>
-      <c r="E29" s="23" t="n"/>
-      <c r="F29" s="23" t="n"/>
-      <c r="G29" s="76" t="n"/>
-      <c r="H29" s="126" t="n"/>
-      <c r="I29" s="126" t="n"/>
-      <c r="J29" s="126" t="n"/>
-      <c r="K29" s="24">
+      <c r="B29" s="363" t="n"/>
+      <c r="C29" s="363" t="n"/>
+      <c r="D29" s="363" t="n"/>
+      <c r="E29" s="369" t="n"/>
+      <c r="F29" s="369" t="n"/>
+      <c r="G29" s="363" t="n"/>
+      <c r="H29" s="370" t="n"/>
+      <c r="I29" s="370" t="n"/>
+      <c r="J29" s="370" t="n"/>
+      <c r="K29" s="371">
         <f>IFERROR(J29/I29,"")</f>
         <v/>
       </c>
-      <c r="L29" s="126" t="n"/>
-      <c r="M29" s="126" t="n"/>
-      <c r="N29" s="24">
+      <c r="L29" s="370" t="n"/>
+      <c r="M29" s="370" t="n"/>
+      <c r="N29" s="371">
         <f>IFERROR(M29/L29,"")</f>
         <v/>
       </c>
-      <c r="O29" s="126" t="n"/>
-      <c r="P29" s="126" t="n"/>
-      <c r="Q29" s="76" t="n"/>
+      <c r="O29" s="370" t="n"/>
+      <c r="P29" s="370" t="n"/>
+      <c r="Q29" s="363" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="127">
-      <c r="A30" s="126" t="n">
+      <c r="A30" s="368" t="n">
         <v>11</v>
       </c>
-      <c r="B30" s="76" t="n"/>
-      <c r="C30" s="76" t="n"/>
-      <c r="D30" s="76" t="n"/>
-      <c r="E30" s="23" t="n"/>
-      <c r="F30" s="23" t="n"/>
-      <c r="G30" s="76" t="n"/>
-      <c r="H30" s="126" t="n"/>
-      <c r="I30" s="126" t="n"/>
-      <c r="J30" s="126" t="n"/>
-      <c r="K30" s="24">
+      <c r="B30" s="363" t="n"/>
+      <c r="C30" s="363" t="n"/>
+      <c r="D30" s="363" t="n"/>
+      <c r="E30" s="369" t="n"/>
+      <c r="F30" s="369" t="n"/>
+      <c r="G30" s="363" t="n"/>
+      <c r="H30" s="370" t="n"/>
+      <c r="I30" s="370" t="n"/>
+      <c r="J30" s="370" t="n"/>
+      <c r="K30" s="371">
         <f>IFERROR(J30/I30,"")</f>
         <v/>
       </c>
-      <c r="L30" s="126" t="n"/>
-      <c r="M30" s="126" t="n"/>
-      <c r="N30" s="24">
+      <c r="L30" s="370" t="n"/>
+      <c r="M30" s="370" t="n"/>
+      <c r="N30" s="371">
         <f>IFERROR(M30/L30,"")</f>
         <v/>
       </c>
-      <c r="O30" s="126" t="n"/>
-      <c r="P30" s="126" t="n"/>
-      <c r="Q30" s="76" t="n"/>
+      <c r="O30" s="370" t="n"/>
+      <c r="P30" s="370" t="n"/>
+      <c r="Q30" s="363" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="127">
-      <c r="A31" s="126" t="n">
+      <c r="A31" s="368" t="n">
         <v>12</v>
       </c>
-      <c r="B31" s="76" t="n"/>
-      <c r="C31" s="76" t="n"/>
-      <c r="D31" s="76" t="n"/>
-      <c r="E31" s="23" t="n"/>
-      <c r="F31" s="23" t="n"/>
-      <c r="G31" s="76" t="n"/>
-      <c r="H31" s="126" t="n"/>
-      <c r="I31" s="126" t="n"/>
-      <c r="J31" s="126" t="n"/>
-      <c r="K31" s="24">
+      <c r="B31" s="363" t="n"/>
+      <c r="C31" s="363" t="n"/>
+      <c r="D31" s="363" t="n"/>
+      <c r="E31" s="369" t="n"/>
+      <c r="F31" s="369" t="n"/>
+      <c r="G31" s="363" t="n"/>
+      <c r="H31" s="370" t="n"/>
+      <c r="I31" s="370" t="n"/>
+      <c r="J31" s="370" t="n"/>
+      <c r="K31" s="371">
         <f>IFERROR(J31/I31,"")</f>
         <v/>
       </c>
-      <c r="L31" s="126" t="n"/>
-      <c r="M31" s="126" t="n"/>
-      <c r="N31" s="24">
+      <c r="L31" s="370" t="n"/>
+      <c r="M31" s="370" t="n"/>
+      <c r="N31" s="371">
         <f>IFERROR(M31/L31,"")</f>
         <v/>
       </c>
-      <c r="O31" s="126" t="n"/>
-      <c r="P31" s="126" t="n"/>
-      <c r="Q31" s="76" t="n"/>
+      <c r="O31" s="370" t="n"/>
+      <c r="P31" s="370" t="n"/>
+      <c r="Q31" s="363" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="127">
-      <c r="A32" s="126" t="n">
+      <c r="A32" s="368" t="n">
         <v>13</v>
       </c>
-      <c r="B32" s="76" t="n"/>
-      <c r="C32" s="76" t="n"/>
-      <c r="D32" s="76" t="n"/>
-      <c r="E32" s="23" t="n"/>
-      <c r="F32" s="23" t="n"/>
-      <c r="G32" s="76" t="n"/>
-      <c r="H32" s="126" t="n"/>
-      <c r="I32" s="126" t="n"/>
-      <c r="J32" s="126" t="n"/>
-      <c r="K32" s="24">
+      <c r="B32" s="363" t="n"/>
+      <c r="C32" s="363" t="n"/>
+      <c r="D32" s="363" t="n"/>
+      <c r="E32" s="369" t="n"/>
+      <c r="F32" s="369" t="n"/>
+      <c r="G32" s="363" t="n"/>
+      <c r="H32" s="370" t="n"/>
+      <c r="I32" s="370" t="n"/>
+      <c r="J32" s="370" t="n"/>
+      <c r="K32" s="371">
         <f>IFERROR(J32/I32,"")</f>
         <v/>
       </c>
-      <c r="L32" s="126" t="n"/>
-      <c r="M32" s="126" t="n"/>
-      <c r="N32" s="24">
+      <c r="L32" s="370" t="n"/>
+      <c r="M32" s="370" t="n"/>
+      <c r="N32" s="371">
         <f>IFERROR(M32/L32,"")</f>
         <v/>
       </c>
-      <c r="O32" s="126" t="n"/>
-      <c r="P32" s="126" t="n"/>
-      <c r="Q32" s="76" t="n"/>
+      <c r="O32" s="370" t="n"/>
+      <c r="P32" s="370" t="n"/>
+      <c r="Q32" s="363" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="127">
-      <c r="A33" s="126" t="n">
+      <c r="A33" s="368" t="n">
         <v>14</v>
       </c>
-      <c r="B33" s="76" t="n"/>
-      <c r="C33" s="76" t="n"/>
-      <c r="D33" s="76" t="n"/>
-      <c r="E33" s="23" t="n"/>
-      <c r="F33" s="23" t="n"/>
-      <c r="G33" s="76" t="n"/>
-      <c r="H33" s="126" t="n"/>
-      <c r="I33" s="126" t="n"/>
-      <c r="J33" s="126" t="n"/>
-      <c r="K33" s="24">
+      <c r="B33" s="363" t="n"/>
+      <c r="C33" s="363" t="n"/>
+      <c r="D33" s="363" t="n"/>
+      <c r="E33" s="369" t="n"/>
+      <c r="F33" s="369" t="n"/>
+      <c r="G33" s="363" t="n"/>
+      <c r="H33" s="370" t="n"/>
+      <c r="I33" s="370" t="n"/>
+      <c r="J33" s="370" t="n"/>
+      <c r="K33" s="371">
         <f>IFERROR(J33/I33,"")</f>
         <v/>
       </c>
-      <c r="L33" s="126" t="n"/>
-      <c r="M33" s="126" t="n"/>
-      <c r="N33" s="24">
+      <c r="L33" s="370" t="n"/>
+      <c r="M33" s="370" t="n"/>
+      <c r="N33" s="371">
         <f>IFERROR(M33/L33,"")</f>
         <v/>
       </c>
-      <c r="O33" s="126" t="n"/>
-      <c r="P33" s="126" t="n"/>
-      <c r="Q33" s="76" t="n"/>
+      <c r="O33" s="370" t="n"/>
+      <c r="P33" s="370" t="n"/>
+      <c r="Q33" s="363" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="127">
-      <c r="A34" s="126" t="n">
+      <c r="A34" s="368" t="n">
         <v>15</v>
       </c>
-      <c r="B34" s="76" t="n"/>
-      <c r="C34" s="76" t="n"/>
-      <c r="D34" s="76" t="n"/>
-      <c r="E34" s="23" t="n"/>
-      <c r="F34" s="23" t="n"/>
-      <c r="G34" s="76" t="n"/>
-      <c r="H34" s="126" t="n"/>
-      <c r="I34" s="126" t="n"/>
-      <c r="J34" s="126" t="n"/>
-      <c r="K34" s="24">
+      <c r="B34" s="363" t="n"/>
+      <c r="C34" s="363" t="n"/>
+      <c r="D34" s="363" t="n"/>
+      <c r="E34" s="369" t="n"/>
+      <c r="F34" s="369" t="n"/>
+      <c r="G34" s="363" t="n"/>
+      <c r="H34" s="370" t="n"/>
+      <c r="I34" s="370" t="n"/>
+      <c r="J34" s="370" t="n"/>
+      <c r="K34" s="371">
         <f>IFERROR(J34/I34,"")</f>
         <v/>
       </c>
-      <c r="L34" s="126" t="n"/>
-      <c r="M34" s="126" t="n"/>
-      <c r="N34" s="24">
+      <c r="L34" s="370" t="n"/>
+      <c r="M34" s="370" t="n"/>
+      <c r="N34" s="371">
         <f>IFERROR(M34/L34,"")</f>
         <v/>
       </c>
-      <c r="O34" s="126" t="n"/>
-      <c r="P34" s="126" t="n"/>
-      <c r="Q34" s="76" t="n"/>
+      <c r="O34" s="370" t="n"/>
+      <c r="P34" s="370" t="n"/>
+      <c r="Q34" s="363" t="n"/>
     </row>
     <row r="35" ht="21" customHeight="1" s="127">
       <c r="A35" s="128" t="inlineStr">
@@ -3457,42 +3526,42 @@
       <c r="Q36" s="97" t="n"/>
     </row>
     <row r="37" ht="19.95" customHeight="1" s="127">
-      <c r="A37" s="100" t="n"/>
-      <c r="B37" s="104" t="n"/>
-      <c r="C37" s="104" t="n"/>
-      <c r="D37" s="104" t="n"/>
-      <c r="E37" s="104" t="n"/>
-      <c r="F37" s="104" t="n"/>
-      <c r="G37" s="104" t="n"/>
-      <c r="H37" s="104" t="n"/>
-      <c r="I37" s="104" t="n"/>
-      <c r="J37" s="104" t="n"/>
-      <c r="K37" s="104" t="n"/>
-      <c r="L37" s="104" t="n"/>
-      <c r="M37" s="104" t="n"/>
-      <c r="N37" s="104" t="n"/>
-      <c r="O37" s="104" t="n"/>
-      <c r="P37" s="104" t="n"/>
-      <c r="Q37" s="94" t="n"/>
+      <c r="A37" s="372" t="n"/>
+      <c r="B37" s="373" t="n"/>
+      <c r="C37" s="373" t="n"/>
+      <c r="D37" s="373" t="n"/>
+      <c r="E37" s="373" t="n"/>
+      <c r="F37" s="373" t="n"/>
+      <c r="G37" s="373" t="n"/>
+      <c r="H37" s="373" t="n"/>
+      <c r="I37" s="373" t="n"/>
+      <c r="J37" s="373" t="n"/>
+      <c r="K37" s="373" t="n"/>
+      <c r="L37" s="373" t="n"/>
+      <c r="M37" s="373" t="n"/>
+      <c r="N37" s="373" t="n"/>
+      <c r="O37" s="373" t="n"/>
+      <c r="P37" s="373" t="n"/>
+      <c r="Q37" s="374" t="n"/>
     </row>
     <row r="38" ht="19.95" customHeight="1" s="127">
-      <c r="A38" s="96" t="n"/>
-      <c r="B38" s="98" t="n"/>
-      <c r="C38" s="98" t="n"/>
-      <c r="D38" s="98" t="n"/>
-      <c r="E38" s="98" t="n"/>
-      <c r="F38" s="98" t="n"/>
-      <c r="G38" s="98" t="n"/>
-      <c r="H38" s="98" t="n"/>
-      <c r="I38" s="98" t="n"/>
-      <c r="J38" s="98" t="n"/>
-      <c r="K38" s="98" t="n"/>
-      <c r="L38" s="98" t="n"/>
-      <c r="M38" s="98" t="n"/>
-      <c r="N38" s="98" t="n"/>
-      <c r="O38" s="98" t="n"/>
-      <c r="P38" s="98" t="n"/>
-      <c r="Q38" s="97" t="n"/>
+      <c r="A38" s="375" t="n"/>
+      <c r="B38" s="376" t="n"/>
+      <c r="C38" s="376" t="n"/>
+      <c r="D38" s="376" t="n"/>
+      <c r="E38" s="376" t="n"/>
+      <c r="F38" s="376" t="n"/>
+      <c r="G38" s="376" t="n"/>
+      <c r="H38" s="376" t="n"/>
+      <c r="I38" s="376" t="n"/>
+      <c r="J38" s="376" t="n"/>
+      <c r="K38" s="376" t="n"/>
+      <c r="L38" s="376" t="n"/>
+      <c r="M38" s="376" t="n"/>
+      <c r="N38" s="376" t="n"/>
+      <c r="O38" s="376" t="n"/>
+      <c r="P38" s="376" t="n"/>
+      <c r="Q38" s="377" t="n"/>
     </row>
     <row r="39" ht="16.5" customHeight="1" s="127">
       <c r="A39" s="227" t="inlineStr">
@@ -3540,29 +3609,29 @@
         </is>
       </c>
       <c r="B41" s="97" t="n"/>
-      <c r="C41" s="301" t="n"/>
-      <c r="D41" s="98" t="n"/>
-      <c r="E41" s="98" t="n"/>
-      <c r="F41" s="98" t="n"/>
-      <c r="G41" s="97" t="n"/>
+      <c r="C41" s="378" t="n"/>
+      <c r="D41" s="376" t="n"/>
+      <c r="E41" s="376" t="n"/>
+      <c r="F41" s="376" t="n"/>
+      <c r="G41" s="377" t="n"/>
       <c r="H41" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="I41" s="97" t="n"/>
-      <c r="J41" s="301" t="n"/>
-      <c r="K41" s="98" t="n"/>
-      <c r="L41" s="98" t="n"/>
-      <c r="M41" s="98" t="n"/>
-      <c r="N41" s="97" t="n"/>
+      <c r="J41" s="378" t="n"/>
+      <c r="K41" s="376" t="n"/>
+      <c r="L41" s="376" t="n"/>
+      <c r="M41" s="376" t="n"/>
+      <c r="N41" s="377" t="n"/>
       <c r="O41" s="302" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="P41" s="97" t="n"/>
-      <c r="Q41" s="301" t="n"/>
+      <c r="Q41" s="378" t="n"/>
     </row>
     <row r="42" ht="21" customHeight="1" s="127">
       <c r="A42" s="70" t="inlineStr">
@@ -3571,29 +3640,29 @@
         </is>
       </c>
       <c r="B42" s="89" t="n"/>
-      <c r="C42" s="68" t="n"/>
-      <c r="D42" s="93" t="n"/>
-      <c r="E42" s="93" t="n"/>
-      <c r="F42" s="93" t="n"/>
-      <c r="G42" s="89" t="n"/>
+      <c r="C42" s="363" t="n"/>
+      <c r="D42" s="361" t="n"/>
+      <c r="E42" s="361" t="n"/>
+      <c r="F42" s="361" t="n"/>
+      <c r="G42" s="362" t="n"/>
       <c r="H42" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="I42" s="89" t="n"/>
-      <c r="J42" s="68" t="n"/>
-      <c r="K42" s="93" t="n"/>
-      <c r="L42" s="93" t="n"/>
-      <c r="M42" s="93" t="n"/>
-      <c r="N42" s="89" t="n"/>
+      <c r="J42" s="363" t="n"/>
+      <c r="K42" s="361" t="n"/>
+      <c r="L42" s="361" t="n"/>
+      <c r="M42" s="361" t="n"/>
+      <c r="N42" s="362" t="n"/>
       <c r="O42" s="70" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="P42" s="89" t="n"/>
-      <c r="Q42" s="68" t="n"/>
+      <c r="Q42" s="363" t="n"/>
     </row>
     <row r="43" ht="21" customHeight="1" s="127">
       <c r="A43" s="70" t="inlineStr">
@@ -3602,31 +3671,31 @@
         </is>
       </c>
       <c r="B43" s="89" t="n"/>
-      <c r="C43" s="68" t="n"/>
-      <c r="D43" s="93" t="n"/>
-      <c r="E43" s="93" t="n"/>
-      <c r="F43" s="93" t="n"/>
-      <c r="G43" s="89" t="n"/>
+      <c r="C43" s="363" t="n"/>
+      <c r="D43" s="361" t="n"/>
+      <c r="E43" s="361" t="n"/>
+      <c r="F43" s="361" t="n"/>
+      <c r="G43" s="362" t="n"/>
       <c r="H43" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="I43" s="89" t="n"/>
-      <c r="J43" s="68" t="n"/>
-      <c r="K43" s="93" t="n"/>
-      <c r="L43" s="93" t="n"/>
-      <c r="M43" s="93" t="n"/>
-      <c r="N43" s="89" t="n"/>
+      <c r="J43" s="363" t="n"/>
+      <c r="K43" s="361" t="n"/>
+      <c r="L43" s="361" t="n"/>
+      <c r="M43" s="361" t="n"/>
+      <c r="N43" s="362" t="n"/>
       <c r="O43" s="70" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="P43" s="89" t="n"/>
-      <c r="Q43" s="68" t="n"/>
-    </row>
-    <row r="44" s="106">
+      <c r="Q43" s="363" t="n"/>
+    </row>
+    <row r="44" customFormat="1" s="106">
       <c r="A44" s="25" t="inlineStr">
         <is>
           <t>REV. 04/10/2026</t>
@@ -3638,11 +3707,12 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="68">
+    <mergeCell ref="A9:Q9"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="H13:K13"/>
     <mergeCell ref="E13:G13"/>
-    <mergeCell ref="A9:Q9"/>
-    <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A39:Q39"/>
     <mergeCell ref="O35:Q35"/>
